--- a/outputs/scotland_route_analysis.xlsx
+++ b/outputs/scotland_route_analysis.xlsx
@@ -516,7 +516,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Wick</t>
+          <t>Thurso</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,97 +525,97 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>6870</v>
+        <v>7390</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.3678311499272198</v>
+        <v>0.3825439783491204</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>58.5001982059755</v>
+        <v>92.26918504108117</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.06448958116797346</v>
+        <v>0.07958335045859392</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.5055556617644169</v>
+        <v>0.558595371657481</v>
       </c>
       <c r="H2" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>0.5233484143107967</v>
+        <v>0.5460595740386915</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Largs</t>
+          <t>Wick</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>North Ayrshire</t>
+          <t>Highland</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>11030</v>
+        <v>6870</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.5049864007252947</v>
+        <v>0.3678311499272198</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>12.6451854685197</v>
+        <v>86.26106412973581</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.1624317551545854</v>
+        <v>0.06448958116797346</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>1</v>
+        <v>0.5055556617644169</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>0.2150740256157737</v>
+        <v>0.9348278874592492</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>0.4591685935901196</v>
+        <v>0.5016243767972132</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Thurso</t>
+          <t>Largs</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Highland</t>
+          <t>North Ayrshire</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>7390</v>
+        <v>11030</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.3825439783491204</v>
+        <v>0.5049864007252947</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>43.25856115499002</v>
+        <v>12.6451854685197</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.07958335045859392</v>
+        <v>0.1624317551545854</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.558595371657481</v>
+        <v>1</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.7391003491384204</v>
+        <v>0.1362916396558224</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.4590930237514984</v>
+        <v>0.4329077982701359</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Girvan</t>
+          <t>Ayr</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -624,25 +624,25 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>6330</v>
+        <v>46260</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.4221169036334913</v>
+        <v>0.4049286640726329</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>27.44105371995364</v>
+        <v>0.6619179009214885</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.04755464536811136</v>
+        <v>0.4590085003333255</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.7012556689514113</v>
+        <v>0.6392921080548964</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0.4683432018912613</v>
+        <v>0.006305097433162528</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0.405717838736928</v>
+        <v>0.3682019019404615</v>
       </c>
     </row>
     <row r="6">
@@ -672,82 +672,82 @@
         <v>0.8064559770048159</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.2668800725761551</v>
+        <v>0.1691209460497558</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.3997121407383535</v>
+        <v>0.3671257652295538</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Crieff</t>
+          <t>Glasgow</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Perth and Kinross</t>
+          <t>Glasgow City</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>7280</v>
+        <v>632350</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.4184065934065934</v>
+        <v>0.2509021902427453</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>25.27454962641586</v>
+        <v>0.5352267433794239</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.0764809919089298</v>
+        <v>1</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.6878800098052068</v>
+        <v>0.0840270527220817</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.4312579360695271</v>
+        <v>0.004930835746508065</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.3985396459278879</v>
+        <v>0.3629859628228632</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Forres</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Moray</t>
+          <t>City of Edinburgh</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>9900</v>
+        <v>506520</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.411010101010101</v>
+        <v>0.2604872463081419</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>18.23767646162939</v>
+        <v>0.5385562723413466</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.1400727231614221</v>
+        <v>0.9541005025720467</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.6612156730994075</v>
+        <v>0.1185811560147315</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0.3108038309292068</v>
+        <v>0.004966952269363716</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0.3706974090633455</v>
+        <v>0.3592162036187139</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ayr</t>
+          <t>Troon</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -756,460 +756,460 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>46260</v>
+        <v>14950</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.4049286640726329</v>
+        <v>0.4531772575250836</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.6619179009214885</v>
+        <v>1.112940411813158</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.4590085003333255</v>
+        <v>0.2253384610516898</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.6392921080548964</v>
+        <v>0.8132281675318807</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.00994971291177078</v>
+        <v>0.01119749062430785</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0.3694167737666642</v>
+        <v>0.3499213730692928</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lanark</t>
+          <t>Girvan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>South Lanarkshire</t>
+          <t>South Ayrshire</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>8880</v>
+        <v>6330</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.4093468468468469</v>
+        <v>0.4221169036334913</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>18.97566708157464</v>
+        <v>27.44105371995364</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.1175794088108271</v>
+        <v>0.04755464536811136</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.6552196459747988</v>
+        <v>0.7012556689514113</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.3234364303303573</v>
+        <v>0.2967874094729197</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.3654118283719944</v>
+        <v>0.3485325745974808</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Glasgow</t>
+          <t>Crieff</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Glasgow City</t>
+          <t>Perth and Kinross</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>632350</v>
+        <v>7280</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.2509021902427453</v>
+        <v>0.4184065934065934</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.5352267433794239</v>
+        <v>25.27454962641586</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1</v>
+        <v>0.0764809919089298</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0840270527220817</v>
+        <v>0.6878800098052068</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.007781069303515007</v>
+        <v>0.2732866093579593</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.3639360406751989</v>
+        <v>0.3458825370240319</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nairn</t>
+          <t>Prestwick</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Highland</t>
+          <t>South Ayrshire</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>10190</v>
+        <v>14880</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.4139352306182532</v>
+        <v>0.4471774193548387</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>15.50935071754478</v>
+        <v>0.3928117987499232</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.1460454067358039</v>
+        <v>0.2243675781288914</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.6717607580665551</v>
+        <v>0.7915987658404002</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.264101548773609</v>
+        <v>0.003386012841670709</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.3606359045253227</v>
+        <v>0.3397841189369875</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>East Kilbride</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>City of Edinburgh</t>
+          <t>South Lanarkshire</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>506520</v>
+        <v>75310</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.2604872463081419</v>
+        <v>0.3493559952197584</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.5385562723413466</v>
+        <v>0.4163313016131426</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.9541005025720467</v>
+        <v>0.5598221013121427</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.1185811560147315</v>
+        <v>0.4389527749629515</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0.007838062718382015</v>
+        <v>0.003641136816391285</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.3601732404350533</v>
+        <v>0.3341386710304952</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Troon</t>
+          <t>Forres</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>South Ayrshire</t>
+          <t>Moray</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>14950</v>
+        <v>9900</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0.4531772575250836</v>
+        <v>0.411010101010101</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.112940411813158</v>
+        <v>18.23767646162939</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.2253384610516898</v>
+        <v>0.1400727231614221</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.8132281675318807</v>
+        <v>0.6612156730994075</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0.01767011822182514</v>
+        <v>0.1969552743869126</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0.3520789156017985</v>
+        <v>0.3327478902159141</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Auchterarder</t>
+          <t>Nairn</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Perth and Kinross</t>
+          <t>Highland</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>5840</v>
+        <v>10190</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.4154109589041096</v>
+        <v>0.4139352306182532</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>20.19222724654296</v>
+        <v>15.50935071754478</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.03088748461766604</v>
+        <v>0.1460454067358039</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.6770807548692296</v>
+        <v>0.6717607580665551</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>0.3442609730766904</v>
+        <v>0.1673602054685186</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.3507430708545287</v>
+        <v>0.3283887900902925</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Prestwick</t>
+          <t>Lanark</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>South Ayrshire</t>
+          <t>South Lanarkshire</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>14880</v>
+        <v>8880</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.4471774193548387</v>
+        <v>0.4093468468468469</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.3928117987499232</v>
+        <v>18.97566708157464</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.2243675781288914</v>
+        <v>0.1175794088108271</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.7915987658404002</v>
+        <v>0.6552196459747988</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0.005343272811772311</v>
+        <v>0.2049605073785236</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.3404365389270213</v>
+        <v>0.3259198540547165</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cumbernauld</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>North Lanarkshire</t>
+          <t>Dundee City</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>50530</v>
+        <v>148210</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.3314664555709479</v>
+        <v>0.299116119020309</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>9.048714198900063</v>
+        <v>1.403474912568026</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.4772727000506918</v>
+        <v>0.6998746520059863</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.3744610289924106</v>
+        <v>0.2578381461322558</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0.1535112095325239</v>
+        <v>0.01434901627759687</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0.3350816461918754</v>
+        <v>0.3240206048052796</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>East Kilbride</t>
+          <t>Bearsden</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>South Lanarkshire</t>
+          <t>East Dunbartonshire</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>75310</v>
+        <v>28470</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0.3493559952197584</v>
+        <v>0.3963821566561292</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.4163313016131426</v>
+        <v>0.1138906982773396</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.5598221013121427</v>
+        <v>0.3585897083521521</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.4389527749629515</v>
+        <v>0.6084819700602526</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0.005745869335028001</v>
+        <v>0.0003604616554981226</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>0.3348402485367074</v>
+        <v>0.3224773800226343</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dunoon</t>
+          <t>Cumbernauld</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Argyll and Bute</t>
+          <t>North Lanarkshire</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>7660</v>
+        <v>50530</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0.4336814621409922</v>
+        <v>0.3314664555709479</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>10.18666857641227</v>
+        <v>9.048714198900063</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.08700661848813016</v>
+        <v>0.4772727000506918</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.7429458736279078</v>
+        <v>0.3744610289924106</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>0.1729902129227893</v>
+        <v>0.09727950361664565</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>0.3343142350129424</v>
+        <v>0.316337744219916</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Carnoustie</t>
+          <t>Gourock</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Angus</t>
+          <t>Inverclyde</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>11310</v>
+        <v>10210</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.4104332449160035</v>
+        <v>0.4351616062683644</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>10.23123522885001</v>
+        <v>4.455200054525255</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.1676175924130076</v>
+        <v>0.1464510284963852</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.6591361083139288</v>
+        <v>0.7482817895282715</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>0.1737530853112461</v>
+        <v>0.0474521074653106</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>0.3335022620127275</v>
+        <v>0.314061641829989</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Dunoon</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Dundee City</t>
+          <t>Argyll and Bute</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>148210</v>
+        <v>7660</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0.299116119020309</v>
+        <v>0.4336814621409922</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.403474912568026</v>
+        <v>10.18666857641227</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.6998746520059863</v>
+        <v>0.08700661848813016</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.2578381461322558</v>
+        <v>0.7429458736279078</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>0.02264336024016118</v>
+        <v>0.1096232782929211</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>0.3267853861261344</v>
+        <v>0.313191923469653</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cumnock</t>
+          <t>Carnoustie</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>East Ayrshire</t>
+          <t>Angus</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>8700</v>
+        <v>11310</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0.3583908045977012</v>
+        <v>0.4104332449160035</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>22.6292592098443</v>
+        <v>10.23123522885001</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.1133430758198856</v>
+        <v>0.1676175924130076</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.471523240314937</v>
+        <v>0.6591361083139288</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>0.3859770161918044</v>
+        <v>0.110106707792942</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.3236144441088756</v>
+        <v>0.3122868028399594</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Gourock</t>
+          <t>Greenock</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1218,256 +1218,256 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>10210</v>
+        <v>41280</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.4351616062683644</v>
+        <v>0.3620639534883721</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>4.455200054525255</v>
+        <v>0.9716914476000422</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.1464510284963852</v>
+        <v>0.4354464414948417</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.7482817895282715</v>
+        <v>0.4847649329364057</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>0.07488145129289792</v>
+        <v>0.009665315502036496</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>0.3232047564391848</v>
+        <v>0.3099588966444279</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Bearsden</t>
+          <t>Monifieth</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>East Dunbartonshire</t>
+          <t>Angus</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>28470</v>
+        <v>8860</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0.3963821566561292</v>
+        <v>0.4431151241534989</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.1138906982773396</v>
+        <v>3.374660098784203</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.3585897083521521</v>
+        <v>0.1171129666027944</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.6084819700602526</v>
+        <v>0.7769542017361707</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>0.0005688238803486689</v>
+        <v>0.03573112637330977</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>0.3225468340975844</v>
+        <v>0.3099327649040916</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Monifieth</t>
+          <t>Auchterarder</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Angus</t>
+          <t>Perth and Kinross</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>8860</v>
+        <v>5840</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0.4431151241534989</v>
+        <v>0.4154109589041096</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.374660098784203</v>
+        <v>20.19222724654296</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0.1171129666027944</v>
+        <v>0.03088748461766604</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.7769542017361707</v>
+        <v>0.6770807548692296</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>0.05638524276544189</v>
+        <v>0.2181569455251314</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>0.3168174703681357</v>
+        <v>0.308708395004009</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Greenock</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Inverclyde</t>
+          <t>Aberdeen City</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>41280</v>
+        <v>198590</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0.3620639534883721</v>
+        <v>0.2707084948889672</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.9716914476000422</v>
+        <v>0.1326349734354605</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0.4354464414948417</v>
+        <v>0.7604064714916525</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.4847649329364057</v>
+        <v>0.1554287317442822</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>0.01525228047090068</v>
+        <v>0.0005637871258282975</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>0.311821218300716</v>
+        <v>0.3054663301205876</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Paisley</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aberdeen City</t>
+          <t>Renfrewshire</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>198590</v>
+        <v>77270</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.2707084948889672</v>
+        <v>0.3231784651222984</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.1326349734354605</v>
+        <v>0.3424287780761576</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0.7604064714916525</v>
+        <v>0.5651371057182205</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.1554287317442822</v>
+        <v>0.344582844024352</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>0.0008896801524176148</v>
+        <v>0.002839491235007777</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>0.3055749611294507</v>
+        <v>0.3041864803258601</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Paisley</t>
+          <t>Kirkcaldy and Dysart</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Renfrewshire</t>
+          <t>Fife</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>77270</v>
+        <v>50370</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.3231784651222984</v>
+        <v>0.3420686916815565</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.3424287780761576</v>
+        <v>1.488359015833262</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.5651371057182205</v>
+        <v>0.47661662962846</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.344582844024352</v>
+        <v>0.412682063819907</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>0.004480838385656169</v>
+        <v>0.01526978275559439</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>0.3047335960427429</v>
+        <v>0.3015228254013204</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kirkcaldy and Dysart</t>
+          <t>Rutherglen</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fife</t>
+          <t>South Lanarkshire</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>50370</v>
+        <v>30950</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.3420686916815565</v>
+        <v>0.3713085621970921</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.488359015833262</v>
+        <v>0.7643585335339713</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.47661662962846</v>
+        <v>0.3758676768069865</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.412682063819907</v>
+        <v>0.5180917243543987</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>0.02409636904961623</v>
+        <v>0.007416305502354241</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>0.304465020832661</v>
+        <v>0.3004585688879131</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Rutherglen</t>
+          <t>Dumfries</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>South Lanarkshire</t>
+          <t>Dumfries and Galloway</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>30950</v>
+        <v>33470</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>0.3713085621970921</v>
+        <v>0.3667164625037347</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.7643585335339713</v>
+        <v>0.1658523767468461</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.3758676768069865</v>
+        <v>0.3920605073364953</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.5180917243543987</v>
+        <v>0.5015372163732446</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>0.01170324668201025</v>
+        <v>0.0009241074953523472</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>0.3018875492811318</v>
+        <v>0.2981739437350308</v>
       </c>
     </row>
     <row r="31">
@@ -1497,10 +1497,10 @@
         <v>0.8530181625062858</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>0.05002499490280357</v>
+        <v>0.03170066008462353</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>0.3010143858030297</v>
+        <v>0.2949062741969697</v>
       </c>
     </row>
     <row r="32">
@@ -1530,544 +1530,544 @@
         <v>0.5321605388126062</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>0.04922780138323375</v>
+        <v>0.03119548140675161</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>0.3006229950338828</v>
+        <v>0.2946122217083888</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Annan</t>
+          <t>North Berwick</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Dumfries and Galloway</t>
+          <t>East Lothian</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>8760</v>
+        <v>7840</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>0.3845890410958904</v>
+        <v>0.4418367346938776</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>12.71123926956924</v>
+        <v>0.5833395669660715</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.114764847956816</v>
+        <v>0.09181148812762573</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.5659678177767012</v>
+        <v>0.7723456109115994</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>0.2162047055797603</v>
+        <v>0.005452731760205325</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>0.2989791237710925</v>
+        <v>0.2898699435998101</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Dumfries</t>
+          <t>Perth</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Dumfries and Galloway</t>
+          <t>Perth and Kinross</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>33470</v>
+        <v>47350</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.3667164625037347</v>
+        <v>0.3356282998944034</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.1658523767468461</v>
+        <v>0.9834824734846161</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.3920605073364953</v>
+        <v>0.4638262603165949</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.5015372163732446</v>
+        <v>0.3894644674344431</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>0.001458281077467752</v>
+        <v>0.009793216733929027</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>0.2983520015957359</v>
+        <v>0.2876946481616556</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Penicuik</t>
+          <t>Glenrothes</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Midlothian</t>
+          <t>Fife</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>16150</v>
+        <v>38360</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>0.3618575851393189</v>
+        <v>0.3484880083420229</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>9.797583084696265</v>
+        <v>0.2612994934750416</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0.2413104059443933</v>
+        <v>0.4202700821073722</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.4840209755509854</v>
+        <v>0.4358236844260467</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>0.1663300183121685</v>
+        <v>0.001959454540608002</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>0.2972204666025157</v>
+        <v>0.286017740358009</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Dalgety Bay and Hillend</t>
+          <t>Hawick</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fife</t>
+          <t>Scottish Borders</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>9710</v>
+        <v>10630</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.401956745623069</v>
+        <v>0.4212605832549389</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>7.485591673770176</v>
+        <v>0.2189518018267271</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.1360639555945365</v>
+        <v>0.1547903681571959</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.6285783494307505</v>
+        <v>0.6981686361150647</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>0.1267543644707994</v>
+        <v>0.001500094856162678</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>0.2971322231653621</v>
+        <v>0.2848196997094745</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Carluke</t>
+          <t>Kelso</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>South Lanarkshire</t>
+          <t>Scottish Borders</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>13810</v>
+        <v>6870</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0.3602461984069515</v>
+        <v>0.4459970887918486</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>11.90234151213366</v>
+        <v>0.2794541576213165</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>0.2089301130719787</v>
+        <v>0.06448958116797346</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.4782119303858099</v>
+        <v>0.7873436770944645</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>0.202358348932394</v>
+        <v>0.002156384301566428</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>0.2965001307967275</v>
+        <v>0.2846632141880014</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Beith</t>
+          <t>Milngavie</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>North Ayrshire</t>
+          <t>East Dunbartonshire</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>5940</v>
+        <v>12840</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>0.3919191919191919</v>
+        <v>0.4087227414330218</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>15.24404288078529</v>
+        <v>0.4809797309019141</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0.0343997426983584</v>
+        <v>0.1938644693332933</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.5923929932760355</v>
+        <v>0.6529697475091375</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>0.2595601257132223</v>
+        <v>0.004342400118405482</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>0.2954509538958721</v>
+        <v>0.2837255389869454</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Haddington</t>
+          <t>Helensburgh</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>East Lothian</t>
+          <t>Argyll and Bute</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>10360</v>
+        <v>13230</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>0.3708494208494209</v>
+        <v>0.4054421768707483</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>12.31856796654887</v>
+        <v>0.5300440633483651</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0.1494681023686432</v>
+        <v>0.2000542784280104</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.5164365209372133</v>
+        <v>0.6411433204157958</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>0.2094831306256611</v>
+        <v>0.004874617469407641</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>0.2917959179771725</v>
+        <v>0.2820240721044046</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>North Berwick</t>
+          <t>Dalgety Bay and Hillend</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>East Lothian</t>
+          <t>Fife</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>7840</v>
+        <v>9710</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0.4418367346938776</v>
+        <v>0.401956745623069</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.5833395669660715</v>
+        <v>7.485591673770176</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0.09181148812762573</v>
+        <v>0.1360639555945365</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.7723456109115994</v>
+        <v>0.6285783494307505</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>0.008604643492674008</v>
+        <v>0.08032378674177737</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>0.2909205808439663</v>
+        <v>0.2816553639223548</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ardrossan</t>
+          <t>Hamilton</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>North Ayrshire</t>
+          <t>South Lanarkshire</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>10500</v>
+        <v>54480</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.3813333333333334</v>
+        <v>0.319291483113069</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>9.703316947607291</v>
+        <v>1.405118880686691</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>0.1522448827401059</v>
+        <v>0.4928428455988854</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.5542309993845571</v>
+        <v>0.33057028354195</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>0.1647164119671078</v>
+        <v>0.01436684895387352</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>0.2903974313639236</v>
+        <v>0.2792599926982363</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Perth</t>
+          <t>Penicuik</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Perth and Kinross</t>
+          <t>Midlothian</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>47350</v>
+        <v>16150</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>0.3356282998944034</v>
+        <v>0.3618575851393189</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.9834824734846161</v>
+        <v>9.797583084696265</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.4638262603165949</v>
+        <v>0.2413104059443933</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.3894644674344431</v>
+        <v>0.4840209755509854</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>0.01545411407488263</v>
+        <v>0.1054027368244221</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>0.2895816139419735</v>
+        <v>0.2769113727732669</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Montrose</t>
+          <t>Cumnock</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Angus</t>
+          <t>East Ayrshire</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>11730</v>
+        <v>8700</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>0.3625745950554135</v>
+        <v>0.3583908045977012</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>12.00240134500762</v>
+        <v>22.6292592098443</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>0.1751604551855726</v>
+        <v>0.1133430758198856</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.4866057945164196</v>
+        <v>0.471523240314937</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>0.2040711292180522</v>
+        <v>0.2445922526238557</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>0.2886124596400148</v>
+        <v>0.2764861895862261</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Glenrothes</t>
+          <t>Inverness</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Fife</t>
+          <t>Highland</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>38360</v>
+        <v>47790</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>0.3484880083420229</v>
+        <v>0.3239589872358234</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.2612994934750416</v>
+        <v>0.8559442835618549</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.4202700821073722</v>
+        <v>0.46573969615549</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.4358236844260467</v>
+        <v>0.3473966243036667</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>0.003092102913457511</v>
+        <v>0.008409767001551955</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>0.2863952898156255</v>
+        <v>0.2738486958202362</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Hawick</t>
+          <t>Annan</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Scottish Borders</t>
+          <t>Dumfries and Galloway</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>10630</v>
+        <v>8760</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>0.4212605832549389</v>
+        <v>0.3845890410958904</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.2189518018267271</v>
+        <v>12.71123926956924</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0.1547903681571959</v>
+        <v>0.114764847956816</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.6981686361150647</v>
+        <v>0.5659678177767012</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>0.002367213721510462</v>
+        <v>0.1370081474990011</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>0.285108739331257</v>
+        <v>0.2725802710775062</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Kelso</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Scottish Borders</t>
+          <t>East Ayrshire</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>6870</v>
+        <v>46970</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>0.4459970887918486</v>
+        <v>0.3261230572705983</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.2794541576213165</v>
+        <v>0.09132674483604436</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.06448958116797346</v>
+        <v>0.4621593837827396</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.7873436770944645</v>
+        <v>0.3551980914003587</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>0.003402866483107407</v>
+        <v>0.0001157028474216281</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>0.2850787082485151</v>
+        <v>0.2724910593435066</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Milngavie</t>
+          <t>Irvine</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>East Dunbartonshire</t>
+          <t>North Ayrshire</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>12840</v>
+        <v>34130</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>0.4087227414330218</v>
+        <v>0.3411075300322297</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.4809797309019141</v>
+        <v>1.11493833751209</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>0.1938644693332933</v>
+        <v>0.396100051102915</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.6529697475091375</v>
+        <v>0.409217078462996</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>0.00685249276227327</v>
+        <v>0.01121916279775778</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>0.2845622365349014</v>
+        <v>0.2721787641212229</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Helensburgh</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Argyll and Bute</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>13230</v>
+        <v>35590</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.4054421768707483</v>
+        <v>0.3403484124754144</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.5300440633483651</v>
+        <v>0.5203515485797241</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>0.2000542784280104</v>
+        <v>0.4047652842086955</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.6411433204157958</v>
+        <v>0.4064804615574198</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>0.007692354462313413</v>
+        <v>0.004769479494885202</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>0.2829633177687065</v>
+        <v>0.2720050750870001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Hamilton</t>
+          <t>Carluke</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2076,25 +2076,25 @@
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>54480</v>
+        <v>13810</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>0.319291483113069</v>
+        <v>0.3602461984069515</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>1.405118880686691</v>
+        <v>11.90234151213366</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0.4928428455988854</v>
+        <v>0.2089301130719787</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.33057028354195</v>
+        <v>0.4782119303858099</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>0.02267150096459599</v>
+        <v>0.1282337608880386</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>0.2820282100351438</v>
+        <v>0.2717919347819424</v>
       </c>
     </row>
     <row r="50">
@@ -2124,868 +2124,868 @@
         <v>0.776024179804005</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>0.05677249042156194</v>
+        <v>0.03597652382590482</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>0.2777358428058203</v>
+        <v>0.2708038539406013</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Inverness</t>
+          <t>Ardrossan</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Highland</t>
+          <t>North Ayrshire</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>47790</v>
+        <v>10500</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>0.3239589872358234</v>
+        <v>0.3813333333333334</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>0.8559442835618549</v>
+        <v>9.703316947607291</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>0.46573969615549</v>
+        <v>0.1522448827401059</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.3473966243036667</v>
+        <v>0.5542309993845571</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>0.01327097133824235</v>
+        <v>0.104380200263358</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>0.2754690972657997</v>
+        <v>0.270285360796007</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Irvine</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>North Ayrshire</t>
+          <t>Angus</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>34130</v>
+        <v>23500</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>0.3411075300322297</v>
+        <v>0.3615744680851064</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>1.11493833751209</v>
+        <v>0.7812931078474105</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.396100051102915</v>
+        <v>0.3189021690110689</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.409217078462996</v>
+        <v>0.4830003392742206</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>0.01770431783670607</v>
+        <v>0.007600000537669039</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>0.274340482467539</v>
+        <v>0.2698341696076529</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Erskine</t>
+          <t>Giffnock</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Renfrewshire</t>
+          <t>East Renfrewshire</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>15010</v>
+        <v>12250</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>0.3599600266489008</v>
+        <v>0.4004897959183674</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>7.013426450281601</v>
+        <v>0.0918289519286951</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>0.2261670350497355</v>
+        <v>0.1841335762979217</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.4771802819093005</v>
+        <v>0.6232899993913202</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>0.1186720474896859</v>
+        <v>0.000121150457022692</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>0.2740064548162406</v>
+        <v>0.2691815753820883</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Haddington</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>East Lothian</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>35590</v>
+        <v>10360</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>0.3403484124754144</v>
+        <v>0.3708494208494209</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0.5203515485797241</v>
+        <v>12.31856796654887</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>0.4047652842086955</v>
+        <v>0.1494681023686432</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.4064804615574198</v>
+        <v>0.5164365209372133</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>0.007526442250216378</v>
+        <v>0.132748709526699</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>0.2729240626721105</v>
+        <v>0.2662177776108518</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Beith</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>East Ayrshire</t>
+          <t>North Ayrshire</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>46970</v>
+        <v>5940</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>0.3261230572705983</v>
+        <v>0.3919191919191919</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>0.09132674483604436</v>
+        <v>15.24404288078529</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>0.4621593837827396</v>
+        <v>0.0343997426983584</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.3551980914003587</v>
+        <v>0.5923929932760355</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>0.0001825840325424108</v>
+        <v>0.1644823219421432</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>0.2725133530718802</v>
+        <v>0.2637583526388457</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Wishaw</t>
+          <t>Montrose</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>North Lanarkshire</t>
+          <t>Angus</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>30050</v>
+        <v>11730</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.3304159733777038</v>
+        <v>0.3625745950554135</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>4.429679465618022</v>
+        <v>12.00240134500762</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.3697629607519686</v>
+        <v>0.1751604551855726</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.3706740432966785</v>
+        <v>0.4866057945164196</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>0.0744446010573618</v>
+        <v>0.1293191436200267</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>0.271627201702003</v>
+        <v>0.2636951311073396</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Wishaw</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Angus</t>
+          <t>North Lanarkshire</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>23500</v>
+        <v>30050</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0.3615744680851064</v>
+        <v>0.3304159733777038</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>0.7812931078474105</v>
+        <v>4.429679465618022</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>0.3189021690110689</v>
+        <v>0.3697629607519686</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.4830003392742206</v>
+        <v>0.3706740432966785</v>
       </c>
       <c r="H57" s="5" t="n">
-        <v>0.01199312528960903</v>
+        <v>0.0471752770358118</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>0.2712985445249662</v>
+        <v>0.262537427028153</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Leven</t>
+          <t>Forfar</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Fife</t>
+          <t>Angus</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>9420</v>
+        <v>14120</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>0.3773885350318472</v>
+        <v>0.3859773371104816</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>8.420230241302468</v>
+        <v>0.08066027002043333</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0.1297915002555974</v>
+        <v>0.2135224090529714</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.5400100113122684</v>
+        <v>0.5709726214587726</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>0.142753097096123</v>
+        <v>0</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>0.2708515362213296</v>
+        <v>0.2614983435039147</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Strathaven</t>
+          <t>Erskine</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>South Lanarkshire</t>
+          <t>Renfrewshire</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>8090</v>
+        <v>15010</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>0.3737948084054388</v>
+        <v>0.3599600266489008</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>10.85658718005411</v>
+        <v>7.013426450281601</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>0.09830502288243369</v>
+        <v>0.2261670350497355</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.5270546357560669</v>
+        <v>0.4771802819093005</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>0.1844575854373796</v>
+        <v>0.07520205142101873</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>0.2699390813586268</v>
+        <v>0.2595164561266849</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Larkhall</t>
+          <t>Clydebank</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>South Lanarkshire</t>
+          <t>West Dunbartonshire</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>15030</v>
+        <v>25620</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>0.3588157019294744</v>
+        <v>0.3327478532396565</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>6.473472559230385</v>
+        <v>5.034854419430305</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>0.2264424905253464</v>
+        <v>0.3367698693405443</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.4730549941399216</v>
+        <v>0.3790804644032648</v>
       </c>
       <c r="H60" s="5" t="n">
-        <v>0.109429353861346</v>
+        <v>0.05373981373183946</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>0.2696422795088713</v>
+        <v>0.2565300491585495</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Dingwall</t>
+          <t>Larkhall</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Highland</t>
+          <t>South Lanarkshire</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>5360</v>
+        <v>15030</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>0.3625</v>
+        <v>0.3588157019294744</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>18.09213668772193</v>
+        <v>6.473472559230385</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>0.01314515678936724</v>
+        <v>0.2264424905253464</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.4863368795270557</v>
+        <v>0.4730549941399216</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>0.3083125449819091</v>
+        <v>0.06934498957528329</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>0.2692648604327773</v>
+        <v>0.2562808247468504</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Giffnock</t>
+          <t>Cupar</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>East Renfrewshire</t>
+          <t>Fife</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>12250</v>
+        <v>8960</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>0.4004897959183674</v>
+        <v>0.4058035714285714</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>0.0918289519286951</v>
+        <v>0.2383970707611855</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>0.1841335762979217</v>
+        <v>0.1194347309477255</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.6232899993913202</v>
+        <v>0.6424461468985229</v>
       </c>
       <c r="H62" s="5" t="n">
-        <v>0.0001911805930492967</v>
+        <v>0.001711024242252198</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>0.2692049187607637</v>
+        <v>0.2545306340295002</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Clydebank</t>
+          <t>Coatbridge</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>West Dunbartonshire</t>
+          <t>North Lanarkshire</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>25620</v>
+        <v>43950</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>0.3327478532396565</v>
+        <v>0.3132650739476678</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>5.034854419430305</v>
+        <v>0.6157266311021889</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>0.3367698693405443</v>
+        <v>0.4484117298798935</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.3790804644032648</v>
+        <v>0.3088450934789714</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>0.08480372020129841</v>
+        <v>0.00580404516083243</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>0.2668846846483691</v>
+        <v>0.2543536228398991</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Dunbar</t>
+          <t>Leven</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>East Lothian</t>
+          <t>Fife</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>10270</v>
+        <v>9420</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0.3396299902629016</v>
+        <v>0.3773885350318472</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>14.01894177538579</v>
+        <v>8.420230241302468</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>0.1476631434776704</v>
+        <v>0.1297915002555974</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.4038905512669083</v>
+        <v>0.5400100113122684</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>0.2385893828986767</v>
+        <v>0.09046212630034343</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>0.2633810258810851</v>
+        <v>0.2534212126227364</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Forfar</t>
+          <t>Dunfermline</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Angus</t>
+          <t>Fife</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>14120</v>
+        <v>54990</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>0.3859773371104816</v>
+        <v>0.2958719767230406</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>0.08066027002043333</v>
+        <v>1.816298234692715</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>0.2135224090529714</v>
+        <v>0.4947703681973437</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.5709726214587726</v>
+        <v>0.2461430212137317</v>
       </c>
       <c r="H65" s="5" t="n">
-        <v>0</v>
+        <v>0.01882704999328856</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>0.2614983435039147</v>
+        <v>0.253246813134788</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Dunfermline</t>
+          <t>Peebles</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Fife</t>
+          <t>Scottish Borders</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>54990</v>
+        <v>9000</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>0.2958719767230406</v>
+        <v>0.404</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>1.816298234692715</v>
+        <v>0.173728798988598</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>0.4947703681973437</v>
+        <v>0.1203561891822898</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.2461430212137317</v>
+        <v>0.6359442763811959</v>
       </c>
       <c r="H66" s="5" t="n">
-        <v>0.02970988860909939</v>
+        <v>0.001009545702128213</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>0.2568744260067249</v>
+        <v>0.2524366704218713</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Port Glasgow</t>
+          <t>Airdrie</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Inverclyde</t>
+          <t>North Lanarkshire</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>14200</v>
+        <v>36390</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0.3526056338028169</v>
+        <v>0.3225886232481451</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>6.028789134955737</v>
+        <v>0.5323274913519452</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>0.2146911524533973</v>
+        <v>0.4093637960181474</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.450667713978088</v>
+        <v>0.3424564655340472</v>
       </c>
       <c r="H67" s="5" t="n">
-        <v>0.1018174582526859</v>
+        <v>0.004899386582583612</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>0.2557254415613904</v>
+        <v>0.2522398827115927</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Coatbridge</t>
+          <t>Linlithgow</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>North Lanarkshire</t>
+          <t>West Lothian</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>43950</v>
+        <v>12840</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.3132650739476678</v>
+        <v>0.3802959501557632</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>0.6157266311021889</v>
+        <v>0.2190952324496637</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>0.4484117298798935</v>
+        <v>0.1938644693332933</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.3088450934789714</v>
+        <v>0.550491235607773</v>
       </c>
       <c r="H68" s="5" t="n">
-        <v>0.009159031036300648</v>
+        <v>0.001501650696472442</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>0.2554719514650551</v>
+        <v>0.2486191185458462</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cupar</t>
+          <t>Stonehaven</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Fife</t>
+          <t>Aberdeenshire</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>8960</v>
+        <v>11150</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>0.4058035714285714</v>
+        <v>0.3851121076233184</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>0.2383970707611855</v>
+        <v>1.069985432255087</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>0.1194347309477255</v>
+        <v>0.1646701939289479</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.6424461468985229</v>
+        <v>0.5678534713080273</v>
       </c>
       <c r="H69" s="5" t="n">
-        <v>0.002700069297255961</v>
+        <v>0.01073154348322121</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>0.2548603157145014</v>
+        <v>0.2477517362400655</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Saltcoats</t>
+          <t>Strathaven</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>North Ayrshire</t>
+          <t>South Lanarkshire</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>12250</v>
+        <v>8090</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0.3515102040816326</v>
+        <v>0.3737948084054388</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>7.846816450731714</v>
+        <v>10.85658718005411</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>0.1841335762979217</v>
+        <v>0.09830502288243369</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.4467186925558463</v>
+        <v>0.5270546357560669</v>
       </c>
       <c r="H70" s="5" t="n">
-        <v>0.1329376515991151</v>
+        <v>0.1168901111802625</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>0.254596640150961</v>
+        <v>0.2474165899395877</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Dunblane</t>
+          <t>Newton Mearns</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Stirling</t>
+          <t>East Renfrewshire</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>9310</v>
+        <v>28210</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0.3659505907626208</v>
+        <v>0.3294930875576037</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>8.001039787221139</v>
+        <v>0.6238406512130932</v>
       </c>
       <c r="F71" s="5" t="n">
-        <v>0.1273616406608949</v>
+        <v>0.3566918323649774</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.4987762506500592</v>
+        <v>0.3673470422089971</v>
       </c>
       <c r="H71" s="5" t="n">
-        <v>0.1355775789579808</v>
+        <v>0.005892060671776491</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>0.2539051567563116</v>
+        <v>0.2433103117485836</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Airdrie</t>
+          <t>Port Glasgow</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>North Lanarkshire</t>
+          <t>Inverclyde</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>36390</v>
+        <v>14200</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>0.3225886232481451</v>
+        <v>0.3526056338028169</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>0.5323274913519452</v>
+        <v>6.028789134955737</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>0.4093637960181474</v>
+        <v>0.2146911524533973</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.3424564655340472</v>
+        <v>0.450667713978088</v>
       </c>
       <c r="H72" s="5" t="n">
-        <v>0.007731441180289229</v>
+        <v>0.06452135859323897</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>0.2531839009108279</v>
+        <v>0.2432934083415748</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Peebles</t>
+          <t>Blantyre</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Scottish Borders</t>
+          <t>South Lanarkshire</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>9000</v>
+        <v>16800</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.404</v>
+        <v>0.3532738095238095</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>0.173728798988598</v>
+        <v>1.975965836340661</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>0.1203561891822898</v>
+        <v>0.2494731383720238</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.6359442763811959</v>
+        <v>0.4530764857915542</v>
       </c>
       <c r="H73" s="5" t="n">
-        <v>0.001593106215085012</v>
+        <v>0.02055901828375055</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>0.2526311905928569</v>
+        <v>0.2410362141491095</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Kilbirnie</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>North Ayrshire</t>
+          <t>West Lothian</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>7170</v>
+        <v>56840</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>0.3442119944211994</v>
+        <v>0.2845531315974666</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>15.0876661255305</v>
+        <v>1.099637925497388</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>0.07333139840755165</v>
+        <v>0.5016153816236509</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.4204086648692644</v>
+        <v>0.2053386126683752</v>
       </c>
       <c r="H74" s="5" t="n">
-        <v>0.2568833370774371</v>
+        <v>0.01105319407168587</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>0.2502078001180844</v>
+        <v>0.2393357294545707</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Stonehaven</t>
+          <t>Saltcoats</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Aberdeenshire</t>
+          <t>North Ayrshire</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>11150</v>
+        <v>12250</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.3851121076233184</v>
+        <v>0.3515102040816326</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>1.069985432255087</v>
+        <v>7.846816450731714</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>0.1646701939289479</v>
+        <v>0.1841335762979217</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.5678534713080273</v>
+        <v>0.4467186925558463</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>0.01693483374208204</v>
+        <v>0.08424211364698164</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>0.2498194996596857</v>
+        <v>0.2383647941669166</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Linlithgow</t>
+          <t>Bo'ness</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>West Lothian</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>12840</v>
+        <v>14840</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>0.3802959501557632</v>
+        <v>0.352021563342318</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>0.2190952324496637</v>
+        <v>3.904277849474878</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>0.1938644693332933</v>
+        <v>0.2238107351772709</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.550491235607773</v>
+        <v>0.4485621414196632</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>0.002369668903937508</v>
+        <v>0.04147606862079576</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>0.2489084579483346</v>
+        <v>0.2379496484059099</v>
       </c>
     </row>
     <row r="77">
@@ -3015,148 +3015,148 @@
         <v>0.6010168154317694</v>
       </c>
       <c r="H77" s="5" t="n">
-        <v>0.08405136488005753</v>
+        <v>0.05326304885964198</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>0.2479186480529577</v>
+        <v>0.2376558760461525</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Bo'ness</t>
+          <t>Dunblane</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Stirling</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>14840</v>
+        <v>9310</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0.352021563342318</v>
+        <v>0.3659505907626208</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>3.904277849474878</v>
+        <v>8.001039787221139</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>0.2238107351772709</v>
+        <v>0.1273616406608949</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.4485621414196632</v>
+        <v>0.4987762506500592</v>
       </c>
       <c r="H78" s="5" t="n">
-        <v>0.06545100688140069</v>
+        <v>0.08591502615829928</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>0.2459412944927782</v>
+        <v>0.2373509724897511</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Kilwinning</t>
+          <t>Grangemouth</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>North Ayrshire</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>16100</v>
+        <v>16120</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0.3421739130434783</v>
+        <v>0.3555831265508685</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>4.871619411835656</v>
+        <v>0.8979712905572168</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>0.2406689572703858</v>
+        <v>0.2409257754680113</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.4130613865681135</v>
+        <v>0.4614015679344273</v>
       </c>
       <c r="H79" s="5" t="n">
-        <v>0.08200953501322654</v>
+        <v>0.008865648111481102</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>0.2452466262839086</v>
+        <v>0.2370643305046399</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Blantyre</t>
+          <t>Stranraer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>South Lanarkshire</t>
+          <t>Dumfries and Galloway</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>16800</v>
+        <v>10110</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.3532738095238095</v>
+        <v>0.3841740850642928</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>1.975965836340661</v>
+        <v>0.2416802364721833</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>0.2494731383720238</v>
+        <v>0.1444149192280164</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.4530764857915542</v>
+        <v>0.5644719023141411</v>
       </c>
       <c r="H80" s="5" t="n">
-        <v>0.03244300850852395</v>
+        <v>0.0017466378472985</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>0.2449975442240339</v>
+        <v>0.2368778197964853</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Newton Mearns</t>
+          <t>Dumbarton</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>East Renfrewshire</t>
+          <t>West Dunbartonshire</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>28210</v>
+        <v>20480</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>0.3294930875576037</v>
+        <v>0.34150390625</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>0.6238406512130932</v>
+        <v>0.6048215808244621</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>0.3566918323649774</v>
+        <v>0.2904472734848907</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.3673470422089971</v>
+        <v>0.4106460137428876</v>
       </c>
       <c r="H81" s="5" t="n">
-        <v>0.00929792326991947</v>
+        <v>0.005685754404962235</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>0.244445599281298</v>
+        <v>0.2355930138775802</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Dalry</t>
+          <t>Kilwinning</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3165,31 +3165,31 @@
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>5250</v>
+        <v>16100</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.3758095238095238</v>
+        <v>0.3421739130434783</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>10.91953212846661</v>
+        <v>4.871619411835656</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>0.008855583023040119</v>
+        <v>0.2406689572703858</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.5343176797803342</v>
+        <v>0.4130613865681135</v>
       </c>
       <c r="H82" s="5" t="n">
-        <v>0.1855350494269358</v>
+        <v>0.05196914858669234</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>0.2429027707434367</v>
+        <v>0.2352331641417305</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Cockenzie</t>
+          <t>Dunbar</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3198,256 +3198,256 @@
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>5370</v>
+        <v>10270</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.3916201117318436</v>
+        <v>0.3396299902629016</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>7.170634259736987</v>
+        <v>14.01894177538579</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>0.01353074316683331</v>
+        <v>0.1476631434776704</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.5913148099439912</v>
+        <v>0.4038905512669083</v>
       </c>
       <c r="H83" s="5" t="n">
-        <v>0.1213630617463843</v>
+        <v>0.1511932373359854</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>0.2420695382857362</v>
+        <v>0.234248977360188</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Barrhead</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>West Lothian</t>
+          <t>East Renfrewshire</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>56840</v>
+        <v>17890</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0.2845531315974666</v>
+        <v>0.3386249301285634</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>1.099637925497388</v>
+        <v>3.569658975681762</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>0.5016153816236509</v>
+        <v>0.2624774228792335</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.2053386126683752</v>
+        <v>0.4002673119806381</v>
       </c>
       <c r="H84" s="5" t="n">
-        <v>0.01744241210182204</v>
+        <v>0.03784634491468263</v>
       </c>
       <c r="I84" s="5" t="n">
-        <v>0.2414654687979494</v>
+        <v>0.2335303599248514</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Barrhead</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>East Renfrewshire</t>
+          <t>North Lanarkshire</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>17890</v>
+        <v>32840</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.3386249301285634</v>
+        <v>0.3137941534713763</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>3.569658975681762</v>
+        <v>0.1884964878356464</v>
       </c>
       <c r="F85" s="5" t="n">
-        <v>0.2624774228792335</v>
+        <v>0.3881295722900764</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.4002673119806381</v>
+        <v>0.3107524238469441</v>
       </c>
       <c r="H85" s="5" t="n">
-        <v>0.05972314792161303</v>
+        <v>0.001169735800448174</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>0.2408226275938282</v>
+        <v>0.2333505773124895</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Grangemouth</t>
+          <t>Dingwall</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Highland</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>16120</v>
+        <v>5360</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.3555831265508685</v>
+        <v>0.3625</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>0.8979712905572168</v>
+        <v>18.09213668772193</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>0.2409257754680113</v>
+        <v>0.01314515678936724</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.4614015679344273</v>
+        <v>0.4863368795270557</v>
       </c>
       <c r="H86" s="5" t="n">
-        <v>0.01399037119110384</v>
+        <v>0.1953765554056848</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>0.2387725715311808</v>
+        <v>0.2316195305740359</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Renfrew</t>
+          <t>Lenzie</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Renfrewshire</t>
+          <t>East Dunbartonshire</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>24270</v>
+        <v>8090</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.3189946435929131</v>
+        <v>0.3872682323856613</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>3.562362345781554</v>
+        <v>1.960308539664959</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>0.3255716859386494</v>
+        <v>0.09830502288243369</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.3295001778095653</v>
+        <v>0.5756262957173497</v>
       </c>
       <c r="H87" s="5" t="n">
-        <v>0.0595982474147277</v>
+        <v>0.02038917830947409</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>0.2382233703876475</v>
+        <v>0.2314401656364191</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Renfrew</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Renfrewshire</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>9620</v>
+        <v>24270</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.3723492723492723</v>
+        <v>0.3189946435929131</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>3.411027761567819</v>
+        <v>3.562362345781554</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>0.1341376061499472</v>
+        <v>0.3255716859386494</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.5218434818663834</v>
+        <v>0.3295001778095653</v>
       </c>
       <c r="H88" s="5" t="n">
-        <v>0.05700776844894672</v>
+        <v>0.0377671959108524</v>
       </c>
       <c r="I88" s="5" t="n">
-        <v>0.2376629521550924</v>
+        <v>0.230946353219689</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Stranraer</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Dumfries and Galloway</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>10110</v>
+        <v>9620</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.3841740850642928</v>
+        <v>0.3723492723492723</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>0.2416802364721833</v>
+        <v>3.411027761567819</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>0.1444149192280164</v>
+        <v>0.1341376061499472</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.5644719023141411</v>
+        <v>0.5218434818663834</v>
       </c>
       <c r="H89" s="5" t="n">
-        <v>0.002756269086350443</v>
+        <v>0.03612561866911265</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>0.237214363542836</v>
+        <v>0.2307022355618144</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Dumbarton</t>
+          <t>Kirkintilloch</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>West Dunbartonshire</t>
+          <t>East Dunbartonshire</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>20480</v>
+        <v>21870</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0.34150390625</v>
+        <v>0.3315500685871056</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>0.6048215808244621</v>
+        <v>1.151958365050934</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0.2904472734848907</v>
+        <v>0.3040316179906791</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.4106460137428876</v>
+        <v>0.3747624537078436</v>
       </c>
       <c r="H90" s="5" t="n">
-        <v>0.008972363173749562</v>
+        <v>0.01162073151393779</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>0.2366885501338426</v>
+        <v>0.2301382677374868</v>
       </c>
     </row>
     <row r="91">
@@ -3477,175 +3477,175 @@
         <v>0.3695404498993207</v>
       </c>
       <c r="H91" s="5" t="n">
-        <v>0.0572210260823664</v>
+        <v>0.03626075926753997</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>0.2363920228714123</v>
+        <v>0.2294052672664701</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Lenzie</t>
+          <t>Cockenzie</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>East Dunbartonshire</t>
+          <t>East Lothian</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>8090</v>
+        <v>5370</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.3872682323856613</v>
+        <v>0.3916201117318436</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>1.960308539664959</v>
+        <v>7.170634259736987</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>0.09830502288243369</v>
+        <v>0.01353074316683331</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.5756262957173497</v>
+        <v>0.5913148099439912</v>
       </c>
       <c r="H92" s="5" t="n">
-        <v>0.03217499377871101</v>
+        <v>0.07690733751650397</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>0.2353687707928314</v>
+        <v>0.2272509635424428</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Dyce</t>
+          <t>Bothwell</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Aberdeen City</t>
+          <t>South Lanarkshire</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>6350</v>
+        <v>6870</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.3752755905511811</v>
+        <v>0.3927219796215429</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>7.334827941972149</v>
+        <v>0.6560898850430198</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>0.04820722329608891</v>
+        <v>0.06448958116797346</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.5323928517110691</v>
+        <v>0.5952870409477282</v>
       </c>
       <c r="H93" s="5" t="n">
-        <v>0.1241736571060252</v>
+        <v>0.006241878980617138</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>0.2349245773710611</v>
+        <v>0.2220061670321063</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Balloch and Haldane</t>
+          <t>Elgin</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>West Dunbartonshire</t>
+          <t>Moray</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>6010</v>
+        <v>25040</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.3808652246256239</v>
+        <v>0.3193690095846645</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>6.630571131793879</v>
+        <v>0.1700649926692068</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0.03682331723268942</v>
+        <v>0.3320328728513099</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.552543468656722</v>
+        <v>0.3308497662793641</v>
       </c>
       <c r="H94" s="5" t="n">
-        <v>0.1121184982488918</v>
+        <v>0.0009698031601091291</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>0.233828428046101</v>
+        <v>0.221284147430261</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dalry</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>North Lanarkshire</t>
+          <t>North Ayrshire</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>32840</v>
+        <v>5250</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.3137941534713763</v>
+        <v>0.3758095238095238</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>0.1884964878356464</v>
+        <v>10.91953212846661</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>0.3881295722900764</v>
+        <v>0.008855583023040119</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.3107524238469441</v>
+        <v>0.5343176797803342</v>
       </c>
       <c r="H95" s="5" t="n">
-        <v>0.001845893028689017</v>
+        <v>0.1175728962510597</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>0.2335759630552365</v>
+        <v>0.2202487196848114</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Balloch and Haldane</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Renfrewshire</t>
+          <t>West Dunbartonshire</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>6360</v>
+        <v>6010</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>0.3727987421383648</v>
+        <v>0.3808652246256239</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>7.51688829824507</v>
+        <v>6.630571131793879</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>0.04853274190238906</v>
+        <v>0.03682331723268942</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.5234638193389304</v>
+        <v>0.552543468656722</v>
       </c>
       <c r="H96" s="5" t="n">
-        <v>0.1272900863470869</v>
+        <v>0.07104909074138427</v>
       </c>
       <c r="I96" s="5" t="n">
-        <v>0.2330955491961354</v>
+        <v>0.2201386255435986</v>
       </c>
     </row>
     <row r="97">
@@ -3675,742 +3675,742 @@
         <v>0.3562978527346732</v>
       </c>
       <c r="H97" s="5" t="n">
-        <v>0.1034400359694375</v>
+        <v>0.0655495802804089</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>0.2327369739344615</v>
+        <v>0.2201068220381187</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Kirkintilloch</t>
+          <t>Dyce</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>East Dunbartonshire</t>
+          <t>Aberdeen City</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>21870</v>
+        <v>6350</v>
       </c>
       <c r="D98" s="3" t="n">
-        <v>0.3315500685871056</v>
+        <v>0.3752755905511811</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>1.151958365050934</v>
+        <v>7.334827941972149</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>0.3040316179906791</v>
+        <v>0.04820722329608891</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.3747624537078436</v>
+        <v>0.5323928517110691</v>
       </c>
       <c r="H98" s="5" t="n">
-        <v>0.01833801041365574</v>
+        <v>0.07868840172859454</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>0.2323773607040595</v>
+        <v>0.2197628255785842</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Alexandria</t>
+          <t>Kirriemuir</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>West Dunbartonshire</t>
+          <t>Angus</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>6710</v>
+        <v>6060</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>0.3760059612518629</v>
+        <v>0.3986798679867987</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>5.213588891029625</v>
+        <v>0.2893786878290712</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>0.05961472745164219</v>
+        <v>0.03853722125035505</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.5350258362717325</v>
+        <v>0.6167652136964867</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>0.08786321840882046</v>
+        <v>0.002264039025756897</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>0.2275012607107317</v>
+        <v>0.2191888246575329</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Kilsyth</t>
+          <t>Kilbirnie</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>North Lanarkshire</t>
+          <t>North Ayrshire</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>10380</v>
+        <v>7170</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0.3365125240847784</v>
+        <v>0.3442119944211994</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>7.648947632920608</v>
+        <v>15.0876661255305</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>0.1498670745880089</v>
+        <v>0.07333139840755165</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.3926520934430568</v>
+        <v>0.4204086648692644</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>0.1295506200544967</v>
+        <v>0.1627860505716757</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>0.2240232626951874</v>
+        <v>0.2188420379494972</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Bothwell</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>South Lanarkshire</t>
+          <t>Renfrewshire</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>6870</v>
+        <v>6360</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0.3927219796215429</v>
+        <v>0.3727987421383648</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>0.6560898850430198</v>
+        <v>7.51688829824507</v>
       </c>
       <c r="F101" s="5" t="n">
-        <v>0.06448958116797346</v>
+        <v>0.04853274190238906</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.5952870409477282</v>
+        <v>0.5234638193389304</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>0.009849951494882173</v>
+        <v>0.08066327177587045</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>0.2232088578701946</v>
+        <v>0.2175532776723966</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Broxburn</t>
+          <t>Alexandria</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>West Lothian</t>
+          <t>West Dunbartonshire</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>15970</v>
+        <v>6710</v>
       </c>
       <c r="D102" s="3" t="n">
-        <v>0.3185347526612398</v>
+        <v>0.3760059612518629</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>5.923089655133644</v>
+        <v>5.213588891029625</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>0.2389918221652005</v>
+        <v>0.05961472745164219</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.3278422721439156</v>
+        <v>0.5350258362717325</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>0.1000081409667811</v>
+        <v>0.05567860678708344</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>0.2222807450919657</v>
+        <v>0.2167730568368194</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Elgin</t>
+          <t>Musselburgh</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Moray</t>
+          <t>East Lothian</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>25040</v>
+        <v>21100</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0.3193690095846645</v>
+        <v>0.3246445497630332</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>0.1700649926692068</v>
+        <v>0.4094521110835133</v>
       </c>
       <c r="F103" s="5" t="n">
-        <v>0.3320328728513099</v>
+        <v>0.2966169255482408</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.3308497662793641</v>
+        <v>0.3498680755103319</v>
       </c>
       <c r="H103" s="5" t="n">
-        <v>0.001530390787184712</v>
+        <v>0.003566515918110149</v>
       </c>
       <c r="I103" s="5" t="n">
-        <v>0.2214710099726196</v>
+        <v>0.2166838389922276</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Loanhead</t>
+          <t>Stirling</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Midlothian</t>
+          <t>Stirling</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>6820</v>
+        <v>37910</v>
       </c>
       <c r="D104" s="3" t="n">
-        <v>0.369208211143695</v>
+        <v>0.2892640464257452</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>5.27628130440702</v>
+        <v>0.25860833643799</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>0.0629784931369556</v>
+        <v>0.4178289848360826</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.5105199640272038</v>
+        <v>0.222321448915612</v>
       </c>
       <c r="H104" s="5" t="n">
-        <v>0.08893635961452673</v>
+        <v>0.001930262653182374</v>
       </c>
       <c r="I104" s="5" t="n">
-        <v>0.2208116055928954</v>
+        <v>0.2140268988016256</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Stevenston</t>
+          <t>Kinross</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>North Ayrshire</t>
+          <t>Perth and Kinross</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>9050</v>
+        <v>5610</v>
       </c>
       <c r="D105" s="3" t="n">
-        <v>0.3462983425414365</v>
+        <v>0.3975044563279858</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>6.612447805641248</v>
+        <v>0.499498045337819</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>0.1215022698512237</v>
+        <v>0.02257555129527502</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.4279299446572208</v>
+        <v>0.6125278575878842</v>
       </c>
       <c r="H105" s="5" t="n">
-        <v>0.1118082711092575</v>
+        <v>0.004543274516622536</v>
       </c>
       <c r="I105" s="5" t="n">
-        <v>0.2204134952059006</v>
+        <v>0.2132155611332606</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Kirriemuir</t>
+          <t>Galashiels</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Angus</t>
+          <t>Scottish Borders</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>6060</v>
+        <v>10060</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.3986798679867987</v>
+        <v>0.3629224652087475</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>0.2893786878290712</v>
+        <v>0.188583938034903</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>0.03853722125035505</v>
+        <v>0.1433892997170658</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.6167652136964867</v>
+        <v>0.4878598655545776</v>
       </c>
       <c r="H106" s="5" t="n">
-        <v>0.003572750233619691</v>
+        <v>0.001170684402234283</v>
       </c>
       <c r="I106" s="5" t="n">
-        <v>0.2196250617268205</v>
+        <v>0.2108066165579592</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Musselburgh</t>
+          <t>Broxburn</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>East Lothian</t>
+          <t>West Lothian</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>21100</v>
+        <v>15970</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0.3246445497630332</v>
+        <v>0.3185347526612398</v>
       </c>
       <c r="E107" s="4" t="n">
-        <v>0.4094521110835133</v>
+        <v>5.923089655133644</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>0.2966169255482408</v>
+        <v>0.2389918221652005</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.3498680755103319</v>
+        <v>0.3278422721439156</v>
       </c>
       <c r="H107" s="5" t="n">
-        <v>0.005628114372002259</v>
+        <v>0.06337480070998198</v>
       </c>
       <c r="I107" s="5" t="n">
-        <v>0.2173710384768583</v>
+        <v>0.2100696316730327</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Locharbriggs</t>
+          <t>Loanhead</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Dumfries and Galloway</t>
+          <t>Midlothian</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>5610</v>
+        <v>6820</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>0.3843137254901961</v>
+        <v>0.369208211143695</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>3.75648337729842</v>
+        <v>5.27628130440702</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>0.02257555129527502</v>
+        <v>0.0629784931369556</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.5649753057024542</v>
+        <v>0.5105199640272038</v>
       </c>
       <c r="H108" s="5" t="n">
-        <v>0.06292112599910951</v>
+        <v>0.05635865252523885</v>
       </c>
       <c r="I108" s="5" t="n">
-        <v>0.2168239943322796</v>
+        <v>0.2099523698964661</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Alness</t>
+          <t>Ellon</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Highland</t>
+          <t>Aberdeenshire</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>5950</v>
+        <v>10070</v>
       </c>
       <c r="D109" s="3" t="n">
-        <v>0.3278991596638656</v>
+        <v>0.3611717974180735</v>
       </c>
       <c r="E109" s="4" t="n">
-        <v>14.82952333315378</v>
+        <v>0.4697664455974696</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>0.03474771087395882</v>
+        <v>0.1435948308135738</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0.3616009361136871</v>
+        <v>0.4815487125203817</v>
       </c>
       <c r="H109" s="5" t="n">
-        <v>0.2524645621008235</v>
+        <v>0.004220765833310982</v>
       </c>
       <c r="I109" s="5" t="n">
-        <v>0.2162710696961565</v>
+        <v>0.2097881030557555</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Methil</t>
+          <t>Viewpark</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Fife</t>
+          <t>North Lanarkshire</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>10890</v>
+        <v>15830</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0.3281910009182736</v>
+        <v>0.3272899557801642</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>7.39677756681305</v>
+        <v>3.058178134227458</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>0.1597892571405541</v>
+        <v>0.2371703396784087</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.3626530231104735</v>
+        <v>0.359404757627085</v>
       </c>
       <c r="H110" s="5" t="n">
-        <v>0.1252340835837015</v>
+        <v>0.03229813983466312</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>0.215892121278243</v>
+        <v>0.2096244123800522</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Viewpark</t>
+          <t>Locharbriggs</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>North Lanarkshire</t>
+          <t>Dumfries and Galloway</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>15830</v>
+        <v>5610</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0.3272899557801642</v>
+        <v>0.3843137254901961</v>
       </c>
       <c r="E111" s="4" t="n">
-        <v>3.058178134227458</v>
+        <v>3.75648337729842</v>
       </c>
       <c r="F111" s="5" t="n">
-        <v>0.2371703396784087</v>
+        <v>0.02257555129527502</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.359404757627085</v>
+        <v>0.5649753057024542</v>
       </c>
       <c r="H111" s="5" t="n">
-        <v>0.05096784345455208</v>
+        <v>0.03987289216750629</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>0.2158476469200152</v>
+        <v>0.2091412497217452</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Burntisland</t>
+          <t>Peterhead</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Fife</t>
+          <t>Aberdeenshire</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>6630</v>
+        <v>19060</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0.3580693815987934</v>
+        <v>0.3213536201469045</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>6.917008110513353</v>
+        <v>1.318340735344796</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>0.057133533909265</v>
+        <v>0.2755824494781857</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0.4703645112027527</v>
+        <v>0.338004282423604</v>
       </c>
       <c r="H112" s="5" t="n">
-        <v>0.1170216006841334</v>
+        <v>0.01342553716309047</v>
       </c>
       <c r="I112" s="5" t="n">
-        <v>0.2148398819320504</v>
+        <v>0.2090040896882934</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Bonnyrigg</t>
+          <t>Kilsyth</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Midlothian</t>
+          <t>North Lanarkshire</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>18320</v>
+        <v>10380</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>0.3174672489082969</v>
+        <v>0.3365125240847784</v>
       </c>
       <c r="E113" s="4" t="n">
-        <v>3.119078299505464</v>
+        <v>7.648947632920608</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>0.2673908172629546</v>
+        <v>0.1498670745880089</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.3239939237677755</v>
+        <v>0.3926520934430568</v>
       </c>
       <c r="H113" s="5" t="n">
-        <v>0.05201030574421912</v>
+        <v>0.08209576388921636</v>
       </c>
       <c r="I113" s="5" t="n">
-        <v>0.2144650155916497</v>
+        <v>0.2082049773067607</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Stirling</t>
+          <t>Bonnyrigg</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Stirling</t>
+          <t>Midlothian</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>37910</v>
+        <v>18320</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>0.2892640464257452</v>
+        <v>0.3174672489082969</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>0.25860833643799</v>
+        <v>3.119078299505464</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>0.4178289848360826</v>
+        <v>0.2673908172629546</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.222321448915612</v>
+        <v>0.3239939237677755</v>
       </c>
       <c r="H114" s="5" t="n">
-        <v>0.003046036868909164</v>
+        <v>0.03295874445361374</v>
       </c>
       <c r="I114" s="5" t="n">
-        <v>0.2143988235402012</v>
+        <v>0.2081144951614479</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Kinross</t>
+          <t>Stevenston</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Perth and Kinross</t>
+          <t>North Ayrshire</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>5610</v>
+        <v>9050</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0.3975044563279858</v>
+        <v>0.3462983425414365</v>
       </c>
       <c r="E115" s="4" t="n">
-        <v>0.499498045337819</v>
+        <v>6.612447805641248</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>0.02257555129527502</v>
+        <v>0.1215022698512237</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.6125278575878842</v>
+        <v>0.4279299446572208</v>
       </c>
       <c r="H115" s="5" t="n">
-        <v>0.007169481137912363</v>
+        <v>0.07085250091420527</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>0.2140909633403572</v>
+        <v>0.2067615718075499</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Shotts</t>
+          <t>Brechin</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>North Lanarkshire</t>
+          <t>Angus</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>8630</v>
+        <v>7230</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0.3163383545770568</v>
+        <v>0.3760719225449516</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>12.37556091628497</v>
+        <v>0.1194394731382358</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>0.1116718962506946</v>
+        <v>0.07505530031403501</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.3199242625094567</v>
+        <v>0.5352636265693743</v>
       </c>
       <c r="H116" s="5" t="n">
-        <v>0.210458710915231</v>
+        <v>0.0004206510866087297</v>
       </c>
       <c r="I116" s="5" t="n">
-        <v>0.2140182898917941</v>
+        <v>0.2035798593233393</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Peterhead</t>
+          <t>Elderslie</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Aberdeenshire</t>
+          <t>Renfrewshire</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>19060</v>
+        <v>5480</v>
       </c>
       <c r="D117" s="3" t="n">
-        <v>0.3213536201469045</v>
+        <v>0.3797445255474453</v>
       </c>
       <c r="E117" s="4" t="n">
-        <v>1.318340735344796</v>
+        <v>4.042867674921821</v>
       </c>
       <c r="F117" s="5" t="n">
-        <v>0.2755824494781857</v>
+        <v>0.01772542577627461</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.338004282423604</v>
+        <v>0.5485033512653208</v>
       </c>
       <c r="H117" s="5" t="n">
-        <v>0.02118607077449368</v>
+        <v>0.04297939916861735</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>0.2115909342254278</v>
+        <v>0.2030693920700709</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Elderslie</t>
+          <t>Methil</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Renfrewshire</t>
+          <t>Fife</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>5480</v>
+        <v>10890</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.3797445255474453</v>
+        <v>0.3281910009182736</v>
       </c>
       <c r="E118" s="4" t="n">
-        <v>4.042867674921821</v>
+        <v>7.39677756681305</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>0.01772542577627461</v>
+        <v>0.1597892571405541</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.5485033512653208</v>
+        <v>0.3626530231104735</v>
       </c>
       <c r="H118" s="5" t="n">
-        <v>0.06782332666247939</v>
+        <v>0.07936039018914041</v>
       </c>
       <c r="I118" s="5" t="n">
-        <v>0.2113507012346916</v>
+        <v>0.2006008901467227</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Galashiels</t>
+          <t>Burntisland</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Scottish Borders</t>
+          <t>Fife</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>10060</v>
+        <v>6630</v>
       </c>
       <c r="D119" s="3" t="n">
-        <v>0.3629224652087475</v>
+        <v>0.3580693815987934</v>
       </c>
       <c r="E119" s="4" t="n">
-        <v>0.188583938034903</v>
+        <v>6.917008110513353</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>0.1433892997170658</v>
+        <v>0.057133533909265</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.4878598655545776</v>
+        <v>0.4703645112027527</v>
       </c>
       <c r="H119" s="5" t="n">
-        <v>0.001847389962802952</v>
+        <v>0.07415616919210041</v>
       </c>
       <c r="I119" s="5" t="n">
-        <v>0.2110321850781487</v>
+        <v>0.2005514047680394</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Ellon</t>
+          <t>Fraserburgh</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4419,124 +4419,124 @@
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>10070</v>
+        <v>12570</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>0.3611717974180735</v>
+        <v>0.337629276054097</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>0.4697664455974696</v>
+        <v>1.114476758841491</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>0.1435948308135738</v>
+        <v>0.1894680741524445</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.4815487125203817</v>
+        <v>0.3966779815168276</v>
       </c>
       <c r="H120" s="5" t="n">
-        <v>0.006660548667872222</v>
+        <v>0.01121415589834438</v>
       </c>
       <c r="I120" s="5" t="n">
-        <v>0.2106013640006092</v>
+        <v>0.1991200705225388</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Stonehouse</t>
+          <t>Buckie</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>South Lanarkshire</t>
+          <t>Moray</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>5550</v>
+        <v>9010</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0.3491891891891892</v>
+        <v>0.3573806881243063</v>
       </c>
       <c r="E121" s="4" t="n">
-        <v>9.452733888444458</v>
+        <v>0.3446310757659057</v>
       </c>
       <c r="F121" s="5" t="n">
-        <v>0.02035115317890945</v>
+        <v>0.1205859138384557</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.4383514396373364</v>
+        <v>0.467881772938935</v>
       </c>
       <c r="H121" s="5" t="n">
-        <v>0.1604270411843819</v>
+        <v>0.002863380300324932</v>
       </c>
       <c r="I121" s="5" t="n">
-        <v>0.2063765446668759</v>
+        <v>0.1971103556925718</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Stewarton</t>
+          <t>Inverurie</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>East Ayrshire</t>
+          <t>Aberdeenshire</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
-        <v>7770</v>
+        <v>14660</v>
       </c>
       <c r="D122" s="3" t="n">
-        <v>0.3342342342342342</v>
+        <v>0.3257162346521146</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>8.128542800269216</v>
+        <v>0.5068929413111346</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>0.08995616599072738</v>
+        <v>0.2212862248172945</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.384438864194403</v>
+        <v>0.3537314968718592</v>
       </c>
       <c r="H122" s="5" t="n">
-        <v>0.1377601195523254</v>
+        <v>0.004623489445667988</v>
       </c>
       <c r="I122" s="5" t="n">
-        <v>0.2040517165791519</v>
+        <v>0.1932137370449405</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Brechin</t>
+          <t>Alloa</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Angus</t>
+          <t>Clackmannanshire</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>7230</v>
+        <v>14440</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>0.3760719225449516</v>
+        <v>0.325415512465374</v>
       </c>
       <c r="E123" s="4" t="n">
-        <v>0.1194394731382358</v>
+        <v>0.6434557002680334</v>
       </c>
       <c r="F123" s="5" t="n">
-        <v>0.07505530031403501</v>
+        <v>0.2181582788343633</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.5352636265693743</v>
+        <v>0.352647394136087</v>
       </c>
       <c r="H123" s="5" t="n">
-        <v>0.0006638053721054052</v>
+        <v>0.006104831720056653</v>
       </c>
       <c r="I123" s="5" t="n">
-        <v>0.2036609107518382</v>
+        <v>0.1923035015635023</v>
       </c>
     </row>
     <row r="124">
@@ -4566,16 +4566,16 @@
         <v>0.3157990635772474</v>
       </c>
       <c r="H124" s="5" t="n">
-        <v>0.1112360925308263</v>
+        <v>0.07048991339854849</v>
       </c>
       <c r="I124" s="5" t="n">
-        <v>0.2029303080846327</v>
+        <v>0.1893482483738735</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Fraserburgh</t>
+          <t>Banchory</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4584,388 +4584,388 @@
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>12570</v>
+        <v>7440</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0.337629276054097</v>
+        <v>0.3604838709677419</v>
       </c>
       <c r="E125" s="4" t="n">
-        <v>1.114476758841491</v>
+        <v>0.6713451537113392</v>
       </c>
       <c r="F125" s="5" t="n">
-        <v>0.1894680741524445</v>
+        <v>0.08097827841182566</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.3966779815168276</v>
+        <v>0.479068739376738</v>
       </c>
       <c r="H125" s="5" t="n">
-        <v>0.01769641673568907</v>
+        <v>0.006407358021595439</v>
       </c>
       <c r="I125" s="5" t="n">
-        <v>0.201280824134987</v>
+        <v>0.188818125270053</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Buckie</t>
+          <t>Cambuslang</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Moray</t>
+          <t>South Lanarkshire</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>9010</v>
+        <v>30790</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>0.3573806881243063</v>
+        <v>0.2698928223449172</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>0.3446310757659057</v>
+        <v>3.593196220296792</v>
       </c>
       <c r="F126" s="5" t="n">
-        <v>0.1205859138384557</v>
+        <v>0.3747954772878559</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.467881772938935</v>
+        <v>0.152488234250289</v>
       </c>
       <c r="H126" s="5" t="n">
-        <v>0.004518536350541864</v>
+        <v>0.03810166134016489</v>
       </c>
       <c r="I126" s="5" t="n">
-        <v>0.1976620743759775</v>
+        <v>0.1884617909594366</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Neilston</t>
+          <t>Shotts</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>East Renfrewshire</t>
+          <t>North Lanarkshire</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>5170</v>
+        <v>8630</v>
       </c>
       <c r="D127" s="3" t="n">
-        <v>0.3615087040618956</v>
+        <v>0.3163383545770568</v>
       </c>
       <c r="E127" s="4" t="n">
-        <v>5.989438498083407</v>
+        <v>12.37556091628497</v>
       </c>
       <c r="F127" s="5" t="n">
-        <v>0.005679059470921735</v>
+        <v>0.1116718962506946</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.4827632601339982</v>
+        <v>0.3199242625094567</v>
       </c>
       <c r="H127" s="5" t="n">
-        <v>0.1011438713284711</v>
+        <v>0.1333669312617538</v>
       </c>
       <c r="I127" s="5" t="n">
-        <v>0.1965287303111303</v>
+        <v>0.1883210300073017</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Cambuslang</t>
+          <t>Cowdenbeath and Lumphinnans</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>South Lanarkshire</t>
+          <t>Fife</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>30790</v>
+        <v>12030</v>
       </c>
       <c r="D128" s="3" t="n">
-        <v>0.2698928223449172</v>
+        <v>0.3318370739817124</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>3.593196220296792</v>
+        <v>0.5988460558271254</v>
       </c>
       <c r="F128" s="5" t="n">
-        <v>0.3747954772878559</v>
+        <v>0.1803846477551939</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.152488234250289</v>
+        <v>0.3757971074420656</v>
       </c>
       <c r="H128" s="5" t="n">
-        <v>0.0601260481403863</v>
+        <v>0.005620935871287071</v>
       </c>
       <c r="I128" s="5" t="n">
-        <v>0.195803253226177</v>
+        <v>0.1872675636895155</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Inverurie</t>
+          <t>Stewarton</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Aberdeenshire</t>
+          <t>East Ayrshire</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>14660</v>
+        <v>7770</v>
       </c>
       <c r="D129" s="3" t="n">
-        <v>0.3257162346521146</v>
+        <v>0.3342342342342342</v>
       </c>
       <c r="E129" s="4" t="n">
-        <v>0.5068929413111346</v>
+        <v>8.128542800269216</v>
       </c>
       <c r="F129" s="5" t="n">
-        <v>0.2212862248172945</v>
+        <v>0.08995616599072738</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.3537314968718592</v>
+        <v>0.384438864194403</v>
       </c>
       <c r="H129" s="5" t="n">
-        <v>0.007296063720291268</v>
+        <v>0.08729809431526042</v>
       </c>
       <c r="I129" s="5" t="n">
-        <v>0.1941045951364816</v>
+        <v>0.1872310415001303</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Linwood</t>
+          <t>Stonehouse</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Renfrewshire</t>
+          <t>South Lanarkshire</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>8450</v>
+        <v>5550</v>
       </c>
       <c r="D130" s="3" t="n">
-        <v>0.3357396449704142</v>
+        <v>0.3491891891891892</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>5.032047337131021</v>
+        <v>9.452733888444458</v>
       </c>
       <c r="F130" s="5" t="n">
-        <v>0.1073115397753818</v>
+        <v>0.02035115317890945</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.3898658661567203</v>
+        <v>0.4383514396373364</v>
       </c>
       <c r="H130" s="5" t="n">
-        <v>0.08475566979901071</v>
+        <v>0.1016620413625064</v>
       </c>
       <c r="I130" s="5" t="n">
-        <v>0.1939776919103709</v>
+        <v>0.1867882113929174</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Alloa</t>
+          <t>Alness</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Clackmannanshire</t>
+          <t>Highland</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>14440</v>
+        <v>5950</v>
       </c>
       <c r="D131" s="3" t="n">
-        <v>0.325415512465374</v>
+        <v>0.3278991596638656</v>
       </c>
       <c r="E131" s="4" t="n">
-        <v>0.6434557002680334</v>
+        <v>14.82952333315378</v>
       </c>
       <c r="F131" s="5" t="n">
-        <v>0.2181582788343633</v>
+        <v>0.03474771087395882</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.352647394136087</v>
+        <v>0.3616009361136871</v>
       </c>
       <c r="H131" s="5" t="n">
-        <v>0.009633685067221667</v>
+        <v>0.1599858886966724</v>
       </c>
       <c r="I131" s="5" t="n">
-        <v>0.1934797860125573</v>
+        <v>0.1854448452281061</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Rosyth</t>
+          <t>Neilston</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Fife</t>
+          <t>East Renfrewshire</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
-        <v>13570</v>
+        <v>5170</v>
       </c>
       <c r="D132" s="3" t="n">
-        <v>0.3069270449521002</v>
+        <v>0.3615087040618956</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>4.745327387171643</v>
+        <v>5.989438498083407</v>
       </c>
       <c r="F132" s="5" t="n">
-        <v>0.2053034250364014</v>
+        <v>0.005679059470921735</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>0.2859965147027563</v>
+        <v>0.4827632601339982</v>
       </c>
       <c r="H132" s="5" t="n">
-        <v>0.07984772358632915</v>
+        <v>0.06409450897209522</v>
       </c>
       <c r="I132" s="5" t="n">
-        <v>0.1903825544418289</v>
+        <v>0.184178942859005</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Banchory</t>
+          <t>Linwood</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Aberdeenshire</t>
+          <t>Renfrewshire</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>7440</v>
+        <v>8450</v>
       </c>
       <c r="D133" s="3" t="n">
-        <v>0.3604838709677419</v>
+        <v>0.3357396449704142</v>
       </c>
       <c r="E133" s="4" t="n">
-        <v>0.6713451537113392</v>
+        <v>5.032047337131021</v>
       </c>
       <c r="F133" s="5" t="n">
-        <v>0.08097827841182566</v>
+        <v>0.1073115397753818</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0.479068739376738</v>
+        <v>0.3898658661567203</v>
       </c>
       <c r="H133" s="5" t="n">
-        <v>0.01011108448578401</v>
+        <v>0.0537093643640222</v>
       </c>
       <c r="I133" s="5" t="n">
-        <v>0.1900527007581159</v>
+        <v>0.1836289234320414</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Cowdenbeath and Lumphinnans</t>
+          <t>Dalkeith</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Fife</t>
+          <t>Midlothian</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>12030</v>
+        <v>14330</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0.3318370739817124</v>
+        <v>0.317794836008374</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>0.5988460558271254</v>
+        <v>0.5125836132056162</v>
       </c>
       <c r="F134" s="5" t="n">
-        <v>0.1803846477551939</v>
+        <v>0.2165763890628752</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.3757971074420656</v>
+        <v>0.3251748744493547</v>
       </c>
       <c r="H134" s="5" t="n">
-        <v>0.008870076760531304</v>
+        <v>0.004685218081727777</v>
       </c>
       <c r="I134" s="5" t="n">
-        <v>0.1883506106525969</v>
+        <v>0.1821454938646526</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Bishopton</t>
+          <t>Mayfield</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Renfrewshire</t>
+          <t>Midlothian</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>7920</v>
+        <v>13690</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>0.3296717171717172</v>
+        <v>0.3129291453615778</v>
       </c>
       <c r="E135" s="4" t="n">
-        <v>5.968590233228469</v>
+        <v>2.875798547071807</v>
       </c>
       <c r="F135" s="5" t="n">
-        <v>0.09391167907627397</v>
+        <v>0.2071247166096604</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.3679910015239025</v>
+        <v>0.3076340717610481</v>
       </c>
       <c r="H135" s="5" t="n">
-        <v>0.1007869998845751</v>
+        <v>0.03031980698240663</v>
       </c>
       <c r="I135" s="5" t="n">
-        <v>0.1875632268282506</v>
+        <v>0.181692865117705</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Mayfield</t>
+          <t>Rosyth</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Midlothian</t>
+          <t>Fife</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>13690</v>
+        <v>13570</v>
       </c>
       <c r="D136" s="3" t="n">
-        <v>0.3129291453615778</v>
+        <v>0.3069270449521002</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>2.875798547071807</v>
+        <v>4.745327387171643</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>0.2071247166096604</v>
+        <v>0.2053034250364014</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>0.3076340717610481</v>
+        <v>0.2859965147027563</v>
       </c>
       <c r="H136" s="5" t="n">
-        <v>0.04784594975940522</v>
+        <v>0.0505992164288924</v>
       </c>
       <c r="I136" s="5" t="n">
-        <v>0.1875349127100379</v>
+        <v>0.1806330520560167</v>
       </c>
     </row>
     <row r="137">
@@ -4995,379 +4995,379 @@
         <v>0.3052634077612552</v>
       </c>
       <c r="H137" s="5" t="n">
-        <v>0.08644957266558823</v>
+        <v>0.05478278454315617</v>
       </c>
       <c r="I137" s="5" t="n">
-        <v>0.1875323207513746</v>
+        <v>0.1769767247105639</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Tranent</t>
+          <t>Uddingston</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>East Lothian</t>
+          <t>South Lanarkshire</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>11910</v>
+        <v>6300</v>
       </c>
       <c r="D138" s="3" t="n">
-        <v>0.3042821158690177</v>
+        <v>0.3557142857142857</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>6.214920069176097</v>
+        <v>2.111095779940971</v>
       </c>
       <c r="F138" s="5" t="n">
-        <v>0.1783107754325043</v>
+        <v>0.04657190227704221</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>0.2764615519320626</v>
+        <v>0.4618743963925578</v>
       </c>
       <c r="H138" s="5" t="n">
-        <v>0.1050035658597747</v>
+        <v>0.02202481832704107</v>
       </c>
       <c r="I138" s="5" t="n">
-        <v>0.1865919644081139</v>
+        <v>0.176823705665547</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Fort William</t>
+          <t>Bishopton</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Highland</t>
+          <t>Renfrewshire</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>5600</v>
+        <v>7920</v>
       </c>
       <c r="D139" s="3" t="n">
-        <v>0.3032142857142857</v>
+        <v>0.3296717171717172</v>
       </c>
       <c r="E139" s="4" t="n">
-        <v>15.27167901854122</v>
+        <v>5.968590233228469</v>
       </c>
       <c r="F139" s="5" t="n">
-        <v>0.02220647531580758</v>
+        <v>0.09391167907627397</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>0.2726120268782843</v>
+        <v>0.3679910015239025</v>
       </c>
       <c r="H139" s="5" t="n">
-        <v>0.2600331889850719</v>
+        <v>0.06386836081638156</v>
       </c>
       <c r="I139" s="5" t="n">
-        <v>0.1849505637263879</v>
+        <v>0.1752570138055194</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Dalkeith</t>
+          <t>Tranent</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Midlothian</t>
+          <t>East Lothian</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
-        <v>14330</v>
+        <v>11910</v>
       </c>
       <c r="D140" s="3" t="n">
-        <v>0.317794836008374</v>
+        <v>0.3042821158690177</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>0.5125836132056162</v>
+        <v>6.214920069176097</v>
       </c>
       <c r="F140" s="5" t="n">
-        <v>0.2165763890628752</v>
+        <v>0.1783107754325043</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>0.3251748744493547</v>
+        <v>0.2764615519320626</v>
       </c>
       <c r="H140" s="5" t="n">
-        <v>0.007393474143165894</v>
+        <v>0.06654038357148431</v>
       </c>
       <c r="I140" s="5" t="n">
-        <v>0.1830482458851319</v>
+        <v>0.1737709036453504</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Uddingston</t>
+          <t>Sauchie</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>South Lanarkshire</t>
+          <t>Clackmannanshire</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>6300</v>
+        <v>6310</v>
       </c>
       <c r="D141" s="3" t="n">
-        <v>0.3557142857142857</v>
+        <v>0.35229793977813</v>
       </c>
       <c r="E141" s="4" t="n">
-        <v>2.111095779940971</v>
+        <v>1.669755830363767</v>
       </c>
       <c r="F141" s="5" t="n">
-        <v>0.04657190227704221</v>
+        <v>0.04690000231666699</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>0.4618743963925578</v>
+        <v>0.4495584777838474</v>
       </c>
       <c r="H141" s="5" t="n">
-        <v>0.03475610355128947</v>
+        <v>0.01723745514194597</v>
       </c>
       <c r="I141" s="5" t="n">
-        <v>0.1810674674069631</v>
+        <v>0.1712319784141535</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Bonnybridge</t>
+          <t>Bridge of Allan</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Stirling</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>5200</v>
+        <v>5320</v>
       </c>
       <c r="D142" s="3" t="n">
-        <v>0.3453846153846154</v>
+        <v>0.3530075187969925</v>
       </c>
       <c r="E142" s="4" t="n">
-        <v>6.198065829681246</v>
+        <v>3.824290620066809</v>
       </c>
       <c r="F142" s="5" t="n">
-        <v>0.006875979097111658</v>
+        <v>0.01159558376392886</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>0.424635960527897</v>
+        <v>0.452116508383229</v>
       </c>
       <c r="H142" s="5" t="n">
-        <v>0.1047150623883277</v>
+        <v>0.04060842018400054</v>
       </c>
       <c r="I142" s="5" t="n">
-        <v>0.1787423340044454</v>
+        <v>0.1681068374437195</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Lossiemouth</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Moray</t>
+          <t>Stirling</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>6840</v>
+        <v>6720</v>
       </c>
       <c r="D143" s="3" t="n">
-        <v>0.3217836257309942</v>
+        <v>0.3407738095238095</v>
       </c>
       <c r="E143" s="4" t="n">
-        <v>7.620610415866042</v>
+        <v>3.133413251087295</v>
       </c>
       <c r="F143" s="5" t="n">
-        <v>0.06358425354526302</v>
+        <v>0.05992279456980988</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0.3395544514854931</v>
+        <v>0.4080140168595843</v>
       </c>
       <c r="H143" s="5" t="n">
-        <v>0.1290655560150374</v>
+        <v>0.03311424050496536</v>
       </c>
       <c r="I143" s="5" t="n">
-        <v>0.1774014203485978</v>
+        <v>0.1670170173114532</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>South Queensferry</t>
+          <t>Oban</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>City of Edinburgh</t>
+          <t>Argyll and Bute</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>10400</v>
+        <v>8140</v>
       </c>
       <c r="D144" s="3" t="n">
-        <v>0.2978846153846154</v>
+        <v>0.3378378378378378</v>
       </c>
       <c r="E144" s="4" t="n">
-        <v>7.374895408180727</v>
+        <v>0.4346241149680476</v>
       </c>
       <c r="F144" s="5" t="n">
-        <v>0.1502652788141776</v>
+        <v>0.09957962353595705</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>0.2533985785864113</v>
+        <v>0.3974298462288449</v>
       </c>
       <c r="H144" s="5" t="n">
-        <v>0.1248595144000781</v>
+        <v>0.003839565128378412</v>
       </c>
       <c r="I144" s="5" t="n">
-        <v>0.176174457266889</v>
+        <v>0.1669496782977268</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Bridge of Allan</t>
+          <t>Bonnybridge</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Stirling</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
-        <v>5320</v>
+        <v>5200</v>
       </c>
       <c r="D145" s="3" t="n">
-        <v>0.3530075187969925</v>
+        <v>0.3453846153846154</v>
       </c>
       <c r="E145" s="4" t="n">
-        <v>3.824290620066809</v>
+        <v>6.198065829681246</v>
       </c>
       <c r="F145" s="5" t="n">
-        <v>0.01159558376392886</v>
+        <v>0.006875979097111658</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>0.452116508383229</v>
+        <v>0.424635960527897</v>
       </c>
       <c r="H145" s="5" t="n">
-        <v>0.06408182060855208</v>
+        <v>0.06635755995502329</v>
       </c>
       <c r="I145" s="5" t="n">
-        <v>0.1759313042519033</v>
+        <v>0.1659564998600106</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Sauchie</t>
+          <t>Lossiemouth</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Clackmannanshire</t>
+          <t>Moray</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>6310</v>
+        <v>6840</v>
       </c>
       <c r="D146" s="3" t="n">
-        <v>0.35229793977813</v>
+        <v>0.3217836257309942</v>
       </c>
       <c r="E146" s="4" t="n">
-        <v>1.669755830363767</v>
+        <v>7.620610415866042</v>
       </c>
       <c r="F146" s="5" t="n">
-        <v>0.04690000231666699</v>
+        <v>0.06358425354526302</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>0.4495584777838474</v>
+        <v>0.3395544514854931</v>
       </c>
       <c r="H146" s="5" t="n">
-        <v>0.02720144007447386</v>
+        <v>0.08178838054486912</v>
       </c>
       <c r="I146" s="5" t="n">
-        <v>0.1745533067249961</v>
+        <v>0.1616423618585417</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Kelty</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Stirling</t>
+          <t>Fife</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
-        <v>6720</v>
+        <v>6760</v>
       </c>
       <c r="D147" s="3" t="n">
-        <v>0.3407738095238095</v>
+        <v>0.3337278106508876</v>
       </c>
       <c r="E147" s="4" t="n">
-        <v>3.133413251087295</v>
+        <v>3.850162471853322</v>
       </c>
       <c r="F147" s="5" t="n">
-        <v>0.05992279456980988</v>
+        <v>0.06115049569023388</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>0.4080140168595843</v>
+        <v>0.3826132084351251</v>
       </c>
       <c r="H147" s="5" t="n">
-        <v>0.05225568515131998</v>
+        <v>0.04088906088034275</v>
       </c>
       <c r="I147" s="5" t="n">
-        <v>0.173397498860238</v>
+        <v>0.1615509216685672</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Kelty</t>
+          <t>South Queensferry</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Fife</t>
+          <t>City of Edinburgh</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>6760</v>
+        <v>10400</v>
       </c>
       <c r="D148" s="3" t="n">
-        <v>0.3337278106508876</v>
+        <v>0.2978846153846154</v>
       </c>
       <c r="E148" s="4" t="n">
-        <v>3.850162471853322</v>
+        <v>7.374895408180727</v>
       </c>
       <c r="F148" s="5" t="n">
-        <v>0.06115049569023388</v>
+        <v>0.1502652788141776</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>0.3826132084351251</v>
+        <v>0.2533985785864113</v>
       </c>
       <c r="H148" s="5" t="n">
-        <v>0.06452468360782598</v>
+        <v>0.07912302703915332</v>
       </c>
       <c r="I148" s="5" t="n">
-        <v>0.1694294625777283</v>
+        <v>0.1609289614799141</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Cardenden and Auchterderran</t>
+          <t>Lochgelly</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5376,25 +5376,25 @@
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>5190</v>
+        <v>7300</v>
       </c>
       <c r="D149" s="3" t="n">
-        <v>0.3364161849710983</v>
+        <v>0.3310958904109589</v>
       </c>
       <c r="E149" s="4" t="n">
-        <v>6.416730857608537</v>
+        <v>2.964541231812258</v>
       </c>
       <c r="F149" s="5" t="n">
-        <v>0.006477774870943072</v>
+        <v>0.07704852870281394</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>0.3923047911776851</v>
+        <v>0.3731251425116683</v>
       </c>
       <c r="H149" s="5" t="n">
-        <v>0.1084580743266798</v>
+        <v>0.0312824287941867</v>
       </c>
       <c r="I149" s="5" t="n">
-        <v>0.1690802134584359</v>
+        <v>0.1604853666695563</v>
       </c>
     </row>
     <row r="150">
@@ -5424,142 +5424,142 @@
         <v>0.3757290012394934</v>
       </c>
       <c r="H150" s="5" t="n">
-        <v>0.09389694309569524</v>
+        <v>0.05950215650886661</v>
       </c>
       <c r="I150" s="5" t="n">
-        <v>0.1680085623445157</v>
+        <v>0.1565436334822395</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Oban</t>
+          <t>Cardenden and Auchterderran</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Argyll and Bute</t>
+          <t>Fife</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>8140</v>
+        <v>5190</v>
       </c>
       <c r="D151" s="3" t="n">
-        <v>0.3378378378378378</v>
+        <v>0.3364161849710983</v>
       </c>
       <c r="E151" s="4" t="n">
-        <v>0.4346241149680476</v>
+        <v>6.416730857608537</v>
       </c>
       <c r="F151" s="5" t="n">
-        <v>0.09957962353595705</v>
+        <v>0.006477774870943072</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>0.3974298462288449</v>
+        <v>0.3923047911776851</v>
       </c>
       <c r="H151" s="5" t="n">
-        <v>0.006058997682173767</v>
+        <v>0.06872949321320614</v>
       </c>
       <c r="I151" s="5" t="n">
-        <v>0.1676894891489919</v>
+        <v>0.1558373530872781</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Lochgelly</t>
+          <t>Fort William</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Fife</t>
+          <t>Highland</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
-        <v>7300</v>
+        <v>5600</v>
       </c>
       <c r="D152" s="3" t="n">
-        <v>0.3310958904109589</v>
+        <v>0.3032142857142857</v>
       </c>
       <c r="E152" s="4" t="n">
-        <v>2.964541231812258</v>
+        <v>15.27167901854122</v>
       </c>
       <c r="F152" s="5" t="n">
-        <v>0.07704852870281394</v>
+        <v>0.02220647531580758</v>
       </c>
       <c r="G152" s="5" t="n">
-        <v>0.3731251425116683</v>
+        <v>0.2726120268782843</v>
       </c>
       <c r="H152" s="5" t="n">
-        <v>0.04936500807235762</v>
+        <v>0.1647821004430419</v>
       </c>
       <c r="I152" s="5" t="n">
-        <v>0.1665128930956133</v>
+        <v>0.1532002008790446</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Denny</t>
+          <t>Prestonpans</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>East Lothian</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>8500</v>
+        <v>10460</v>
       </c>
       <c r="D153" s="3" t="n">
-        <v>0.2963529411764706</v>
+        <v>0.2993307839388145</v>
       </c>
       <c r="E153" s="4" t="n">
-        <v>7.872119985597035</v>
+        <v>4.588958827448816</v>
       </c>
       <c r="F153" s="5" t="n">
-        <v>0.1085319977792065</v>
+        <v>0.1514553129586019</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>0.2478768968729375</v>
+        <v>0.2586120126299307</v>
       </c>
       <c r="H153" s="5" t="n">
-        <v>0.1333707863988641</v>
+        <v>0.04890303395812231</v>
       </c>
       <c r="I153" s="5" t="n">
-        <v>0.1632598936836693</v>
+        <v>0.1529901198488849</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Prestonpans</t>
+          <t>Clarkston</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>East Lothian</t>
+          <t>East Renfrewshire</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
-        <v>10460</v>
+        <v>9800</v>
       </c>
       <c r="D154" s="3" t="n">
-        <v>0.2993307839388145</v>
+        <v>0.3147959183673469</v>
       </c>
       <c r="E154" s="4" t="n">
-        <v>4.588958827448816</v>
+        <v>0.4367505969904945</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>0.1514553129586019</v>
+        <v>0.1379725322127736</v>
       </c>
       <c r="G154" s="5" t="n">
-        <v>0.2586120126299307</v>
+        <v>0.3143637838070891</v>
       </c>
       <c r="H154" s="5" t="n">
-        <v>0.0771710752380616</v>
+        <v>0.003862631795598956</v>
       </c>
       <c r="I154" s="5" t="n">
-        <v>0.1624128002755314</v>
+        <v>0.1520663159384872</v>
       </c>
     </row>
     <row r="155">
@@ -5589,148 +5589,148 @@
         <v>0.2920609373104174</v>
       </c>
       <c r="H155" s="5" t="n">
-        <v>0.06576664431798679</v>
+        <v>0.04167608693377387</v>
       </c>
       <c r="I155" s="5" t="n">
-        <v>0.1598527692131221</v>
+        <v>0.1518225834183845</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Clarkston</t>
+          <t>Bathgate</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>East Renfrewshire</t>
+          <t>West Lothian</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
-        <v>9800</v>
+        <v>23600</v>
       </c>
       <c r="D156" s="3" t="n">
-        <v>0.3147959183673469</v>
+        <v>0.2614830508474577</v>
       </c>
       <c r="E156" s="4" t="n">
-        <v>0.4367505969904945</v>
+        <v>0.7531859774318015</v>
       </c>
       <c r="F156" s="5" t="n">
-        <v>0.1379725322127736</v>
+        <v>0.3197805866011029</v>
       </c>
       <c r="G156" s="5" t="n">
-        <v>0.3143637838070891</v>
+        <v>0.1221710289039501</v>
       </c>
       <c r="H156" s="5" t="n">
-        <v>0.006095397867755142</v>
+        <v>0.007295113020644445</v>
       </c>
       <c r="I156" s="5" t="n">
-        <v>0.1528105712958726</v>
+        <v>0.1497489095085658</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Tullibody</t>
+          <t>Denny</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Clackmannanshire</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>8490</v>
+        <v>8500</v>
       </c>
       <c r="D157" s="3" t="n">
-        <v>0.3080094228504123</v>
+        <v>0.2963529411764706</v>
       </c>
       <c r="E157" s="4" t="n">
-        <v>3.54750840189018</v>
+        <v>7.872119985597035</v>
       </c>
       <c r="F157" s="5" t="n">
-        <v>0.1082884815278744</v>
+        <v>0.1085319977792065</v>
       </c>
       <c r="G157" s="5" t="n">
-        <v>0.2898984843359834</v>
+        <v>0.2478768968729375</v>
       </c>
       <c r="H157" s="5" t="n">
-        <v>0.0593439841251471</v>
+        <v>0.08451658961813054</v>
       </c>
       <c r="I157" s="5" t="n">
-        <v>0.1525103166630016</v>
+        <v>0.1469751614234248</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Newmains</t>
+          <t>Tullibody</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>North Lanarkshire</t>
+          <t>Clackmannanshire</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
-        <v>5430</v>
+        <v>8490</v>
       </c>
       <c r="D158" s="3" t="n">
-        <v>0.3152854511970534</v>
+        <v>0.3080094228504123</v>
       </c>
       <c r="E158" s="4" t="n">
-        <v>7.352248959753447</v>
+        <v>3.54750840189018</v>
       </c>
       <c r="F158" s="5" t="n">
-        <v>0.01582928938816022</v>
+        <v>0.1082884815278744</v>
       </c>
       <c r="G158" s="5" t="n">
-        <v>0.3161285484414753</v>
+        <v>0.2898984843359834</v>
       </c>
       <c r="H158" s="5" t="n">
-        <v>0.124471862439323</v>
+        <v>0.03760607017499469</v>
       </c>
       <c r="I158" s="5" t="n">
-        <v>0.1521432334229862</v>
+        <v>0.1452643453462842</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Bathgate</t>
+          <t>Moodiesburn</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>West Lothian</t>
+          <t>North Lanarkshire</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>23600</v>
+        <v>6830</v>
       </c>
       <c r="D159" s="3" t="n">
-        <v>0.2614830508474577</v>
+        <v>0.3092240117130308</v>
       </c>
       <c r="E159" s="4" t="n">
-        <v>0.7531859774318015</v>
+        <v>5.565037706268828</v>
       </c>
       <c r="F159" s="5" t="n">
-        <v>0.3197805866011029</v>
+        <v>0.06328159506901015</v>
       </c>
       <c r="G159" s="5" t="n">
-        <v>0.1221710289039501</v>
+        <v>0.2942770741669324</v>
       </c>
       <c r="H159" s="5" t="n">
-        <v>0.01151199977221068</v>
+        <v>0.05949089054053306</v>
       </c>
       <c r="I159" s="5" t="n">
-        <v>0.1511545384257545</v>
+        <v>0.1390165199254919</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Moodiesburn</t>
+          <t>Newmains</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5739,25 +5739,25 @@
         </is>
       </c>
       <c r="C160" s="2" t="n">
-        <v>6830</v>
+        <v>5430</v>
       </c>
       <c r="D160" s="3" t="n">
-        <v>0.3092240117130308</v>
+        <v>0.3152854511970534</v>
       </c>
       <c r="E160" s="4" t="n">
-        <v>5.565037706268828</v>
+        <v>7.352248959753447</v>
       </c>
       <c r="F160" s="5" t="n">
-        <v>0.06328159506901015</v>
+        <v>0.01582928938816022</v>
       </c>
       <c r="G160" s="5" t="n">
-        <v>0.2942770741669324</v>
+        <v>0.3161285484414753</v>
       </c>
       <c r="H160" s="5" t="n">
-        <v>0.09387916491672493</v>
+        <v>0.07887737338015921</v>
       </c>
       <c r="I160" s="5" t="n">
-        <v>0.1504792780508891</v>
+        <v>0.1369450704032649</v>
       </c>
     </row>
     <row r="161">
@@ -5787,10 +5787,10 @@
         <v>0.2094093579249948</v>
       </c>
       <c r="H161" s="5" t="n">
-        <v>0.103186715693674</v>
+        <v>0.06538905212902929</v>
       </c>
       <c r="I161" s="5" t="n">
-        <v>0.1438561772258911</v>
+        <v>0.1312569560376761</v>
       </c>
     </row>
     <row r="162">
@@ -5820,76 +5820,76 @@
         <v>0.1555953622716542</v>
       </c>
       <c r="H162" s="5" t="n">
-        <v>0.06045942629940185</v>
+        <v>0.03831292188540079</v>
       </c>
       <c r="I162" s="5" t="n">
-        <v>0.1359922767301702</v>
+        <v>0.1286101085921698</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Stepps</t>
+          <t>East Calder</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>North Lanarkshire</t>
+          <t>West Lothian</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>7700</v>
+        <v>6430</v>
       </c>
       <c r="D163" s="3" t="n">
-        <v>0.2905194805194805</v>
+        <v>0.3068429237947123</v>
       </c>
       <c r="E163" s="4" t="n">
-        <v>5.242372365292401</v>
+        <v>3.815766582205486</v>
       </c>
       <c r="F163" s="5" t="n">
-        <v>0.08808405338008772</v>
+        <v>0.05079714171487116</v>
       </c>
       <c r="G163" s="5" t="n">
-        <v>0.2268472857032188</v>
+        <v>0.2856932581394511</v>
       </c>
       <c r="H163" s="5" t="n">
-        <v>0.0883559212832309</v>
+        <v>0.04051595707232267</v>
       </c>
       <c r="I163" s="5" t="n">
-        <v>0.1344290867888458</v>
+        <v>0.125668785642215</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>East Calder</t>
+          <t>Stepps</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>West Lothian</t>
+          <t>North Lanarkshire</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>6430</v>
+        <v>7700</v>
       </c>
       <c r="D164" s="3" t="n">
-        <v>0.3068429237947123</v>
+        <v>0.2905194805194805</v>
       </c>
       <c r="E164" s="4" t="n">
-        <v>3.815766582205486</v>
+        <v>5.242372365292401</v>
       </c>
       <c r="F164" s="5" t="n">
-        <v>0.05079714171487116</v>
+        <v>0.08808405338008772</v>
       </c>
       <c r="G164" s="5" t="n">
-        <v>0.2856932581394511</v>
+        <v>0.2268472857032188</v>
       </c>
       <c r="H164" s="5" t="n">
-        <v>0.06393590987110893</v>
+        <v>0.0559908308337775</v>
       </c>
       <c r="I164" s="5" t="n">
-        <v>0.1334754365751437</v>
+        <v>0.1236407233056947</v>
       </c>
     </row>
     <row r="165">
@@ -5919,10 +5919,10 @@
         <v>0.2604880769037305</v>
       </c>
       <c r="H165" s="5" t="n">
-        <v>0.07272265351655964</v>
+        <v>0.04608408504707531</v>
       </c>
       <c r="I165" s="5" t="n">
-        <v>0.1310445083300333</v>
+        <v>0.1221649855068719</v>
       </c>
     </row>
     <row r="166">
@@ -5952,10 +5952,10 @@
         <v>0.2168997182875541</v>
       </c>
       <c r="H166" s="5" t="n">
-        <v>0.07153370799277459</v>
+        <v>0.04533065452735462</v>
       </c>
       <c r="I166" s="5" t="n">
-        <v>0.1295913525117192</v>
+        <v>0.1208570013565793</v>
       </c>
     </row>
     <row r="167">
@@ -5985,10 +5985,10 @@
         <v>0.3140392041989356</v>
       </c>
       <c r="H167" s="5" t="n">
-        <v>0.07165268437844569</v>
+        <v>0.04540604943679108</v>
       </c>
       <c r="I167" s="5" t="n">
-        <v>0.1295169686311747</v>
+        <v>0.1207680903172898</v>
       </c>
     </row>
     <row r="168">
@@ -6018,10 +6018,10 @@
         <v>0.1281309483289174</v>
       </c>
       <c r="H168" s="5" t="n">
-        <v>0.07334073441622857</v>
+        <v>0.04647576069928223</v>
       </c>
       <c r="I168" s="5" t="n">
-        <v>0.1281399237922832</v>
+        <v>0.1191849325533011</v>
       </c>
     </row>
     <row r="169">
@@ -6051,76 +6051,76 @@
         <v>0.297272224684513</v>
       </c>
       <c r="H169" s="5" t="n">
-        <v>0.05885597569835021</v>
+        <v>0.03729682098293824</v>
       </c>
       <c r="I169" s="5" t="n">
-        <v>0.1244919289089801</v>
+        <v>0.1173055440038428</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Gorebridge</t>
+          <t>Blackburn (West Lothian)</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Midlothian</t>
+          <t>West Lothian</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
-        <v>8040</v>
+        <v>5730</v>
       </c>
       <c r="D170" s="3" t="n">
-        <v>0.2758706467661692</v>
+        <v>0.3036649214659686</v>
       </c>
       <c r="E170" s="4" t="n">
-        <v>5.531727066873062</v>
+        <v>3.215958377426422</v>
       </c>
       <c r="F170" s="5" t="n">
-        <v>0.09702252012851723</v>
+        <v>0.02695385296133569</v>
       </c>
       <c r="G170" s="5" t="n">
-        <v>0.1740382764313641</v>
+        <v>0.2742365676430718</v>
       </c>
       <c r="H170" s="5" t="n">
-        <v>0.09330896801731973</v>
+        <v>0.03400963531190167</v>
       </c>
       <c r="I170" s="5" t="n">
-        <v>0.1214565881924003</v>
+        <v>0.111733351972103</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Blackburn (West Lothian)</t>
+          <t>Gorebridge</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>West Lothian</t>
+          <t>Midlothian</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
-        <v>5730</v>
+        <v>8040</v>
       </c>
       <c r="D171" s="3" t="n">
-        <v>0.3036649214659686</v>
+        <v>0.2758706467661692</v>
       </c>
       <c r="E171" s="4" t="n">
-        <v>3.215958377426422</v>
+        <v>5.531727066873062</v>
       </c>
       <c r="F171" s="5" t="n">
-        <v>0.02695385296133569</v>
+        <v>0.09702252012851723</v>
       </c>
       <c r="G171" s="5" t="n">
-        <v>0.2742365676430718</v>
+        <v>0.1740382764313641</v>
       </c>
       <c r="H171" s="5" t="n">
-        <v>0.05366865638073334</v>
+        <v>0.05912955880777685</v>
       </c>
       <c r="I171" s="5" t="n">
-        <v>0.1182863589950469</v>
+        <v>0.1100634517892194</v>
       </c>
     </row>
     <row r="172">
@@ -6150,10 +6150,10 @@
         <v>0</v>
       </c>
       <c r="H172" s="5" t="n">
-        <v>0.01211900159221754</v>
+        <v>0.007679767899753822</v>
       </c>
       <c r="I172" s="5" t="n">
-        <v>0.09350786629244268</v>
+        <v>0.09202812172828811</v>
       </c>
     </row>
     <row r="173">
@@ -6183,10 +6183,10 @@
         <v>0.1085442478368992</v>
       </c>
       <c r="H173" s="5" t="n">
-        <v>0.05412677886095049</v>
+        <v>0.03429994588665946</v>
       </c>
       <c r="I173" s="5" t="n">
-        <v>0.07837835227527021</v>
+        <v>0.07176940795050653</v>
       </c>
     </row>
     <row r="174">
@@ -6216,10 +6216,10 @@
         <v>0.1019403642437369</v>
       </c>
       <c r="H174" s="5" t="n">
-        <v>0.1017079160709016</v>
+        <v>0.06445194210501305</v>
       </c>
       <c r="I174" s="5" t="n">
-        <v>0.07122753201725407</v>
+        <v>0.05880887402862456</v>
       </c>
     </row>
     <row r="175">
@@ -6249,10 +6249,10 @@
         <v>0.01752387902394242</v>
       </c>
       <c r="H175" s="5" t="n">
-        <v>0.03911466890069912</v>
+        <v>0.02478682557695105</v>
       </c>
       <c r="I175" s="5" t="n">
-        <v>0.03183895085634449</v>
+        <v>0.0270630030817618</v>
       </c>
     </row>
   </sheetData>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Auchterarder</t>
+          <t>Crieff</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -6365,16 +6365,16 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>5840</v>
+        <v>7280</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>74.40000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>74.40000000000001</v>
+        <v>79.7</v>
       </c>
     </row>
     <row r="4">
@@ -6383,25 +6383,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Crieff</t>
+          <t>Thurso</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Perth and Kinross</t>
+          <t>Highland</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>7280</v>
+        <v>7390</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>16.4</v>
+        <v>353.6</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>14</v>
+        <v>271</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>90.8</v>
+        <v>433.3</v>
       </c>
     </row>
     <row r="5">
@@ -6410,7 +6410,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Thurso</t>
+          <t>Wick</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6419,16 +6419,16 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>7390</v>
+        <v>6870</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>353.6</v>
+        <v>34.7</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>271</v>
+        <v>36</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>444.4</v>
+        <v>468</v>
       </c>
     </row>
     <row r="6">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wick</t>
+          <t>Nairn</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6446,16 +6446,16 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>6870</v>
+        <v>10190</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>34.7</v>
+        <v>189.4</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>36</v>
+        <v>152</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>479.2</v>
+        <v>657.5</v>
       </c>
     </row>
     <row r="7">
@@ -6464,25 +6464,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nairn</t>
+          <t>Forres</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Highland</t>
+          <t>Moray</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>10190</v>
+        <v>9900</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>189.4</v>
+        <v>18.2</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>152</v>
+        <v>20</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>668.6</v>
+        <v>675.7</v>
       </c>
     </row>
     <row r="8">
@@ -6491,25 +6491,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Forres</t>
+          <t>Blairgowrie</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Moray</t>
+          <t>Perth and Kinross</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>9900</v>
+        <v>9240</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>18.2</v>
+        <v>161.2</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>686.8</v>
+        <v>836.9</v>
       </c>
     </row>
     <row r="9">
@@ -6518,25 +6518,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Blairgowrie</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Perth and Kinross</t>
+          <t>City of Edinburgh</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>9240</v>
+        <v>506520</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>161.2</v>
+        <v>99.8</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>130</v>
+        <v>81</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>848.1</v>
+        <v>936.8</v>
       </c>
     </row>
     <row r="10">
@@ -6545,25 +6545,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>East Kilbride</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>City of Edinburgh</t>
+          <t>South Lanarkshire</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>506520</v>
+        <v>75310</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>99.8</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>947.9</v>
+        <v>1007.9</v>
       </c>
     </row>
     <row r="11">
@@ -6572,25 +6572,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lanark</t>
+          <t>Girvan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Lanarkshire</t>
+          <t>South Ayrshire</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>8880</v>
+        <v>6330</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>51.6</v>
+        <v>85.7</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>999.5</v>
+        <v>1093.6</v>
       </c>
     </row>
     <row r="12">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Girvan</t>
+          <t>Ayr</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -6608,16 +6608,16 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>6330</v>
+        <v>46260</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>103.1</v>
+        <v>33.6</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1102.6</v>
+        <v>1127.2</v>
       </c>
     </row>
     <row r="13">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ayr</t>
+          <t>Prestwick</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -6635,16 +6635,16 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>46260</v>
+        <v>14880</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>33.6</v>
+        <v>5.9</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1136.2</v>
+        <v>1133.1</v>
       </c>
     </row>
     <row r="14">
@@ -6665,13 +6665,13 @@
         <v>14950</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>17.7</v>
+        <v>9.9</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1153.9</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="15">
@@ -6698,7 +6698,7 @@
         <v>40</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1196.6</v>
+        <v>1185.6</v>
       </c>
     </row>
     <row r="17">
@@ -6708,15 +6708,15 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1247.2</v>
+        <v>1236.3</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>1036</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="18">
       <c r="B18">
-        <f> 17.3 hours driving</f>
+        <f> 16.9 hours driving</f>
         <v/>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Route: closed loop, one town per day, 1,247 km / 17.3 h driving. Entry point Glasgow.</t>
+          <t>Route: closed loop, one town per day, 1,236 km / 16.9 h driving. Entry point Glasgow.</t>
         </is>
       </c>
     </row>
